--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -872,7 +872,7 @@
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
@@ -1144,7 +1144,7 @@
         <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
         <v>2.06</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
         <v>2.68</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
         <v>3.85</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
         <v>2.06</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H6" t="n">
         <v>3.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -890,7 +890,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -890,7 +890,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
         <v>1.76</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
         <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
         <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
         <v>6.4</v>
@@ -1634,7 +1634,7 @@
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.05</v>
@@ -1906,7 +1906,7 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -890,7 +890,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -1126,7 +1126,7 @@
         <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
         <v>2.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
         <v>3.4</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I2" t="n">
         <v>4.5</v>
@@ -875,212 +875,212 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -1129,212 +1129,212 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
         <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
         <v>2.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:28</t>
+          <t>2026-06-08 15:02:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -899,7 +899,7 @@
         <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
@@ -932,7 +932,7 @@
         <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
         <v>13.5</v>
@@ -971,10 +971,10 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
@@ -1007,16 +1007,16 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1028,59 +1028,59 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>4.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
         <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
         <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
         <v>36</v>
       </c>
       <c r="BW2" t="n">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>27</v>
       </c>
       <c r="CA2" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -1129,16 +1129,16 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.04</v>
@@ -1147,16 +1147,16 @@
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>1.77</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1165,130 +1165,130 @@
         <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>1.72</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>21</v>
+        <v>1.96</v>
       </c>
       <c r="BN3" t="n">
         <v>5.9</v>
@@ -1300,41 +1300,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>1.75</v>
       </c>
       <c r="BR3" t="n">
         <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>15.5</v>
+        <v>1.86</v>
       </c>
       <c r="BT3" t="n">
         <v>12</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>1.69</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>21</v>
+        <v>1.91</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>21</v>
+        <v>1.91</v>
       </c>
       <c r="BZ3" t="n">
         <v>26</v>
       </c>
       <c r="CA3" t="n">
-        <v>12</v>
+        <v>1.83</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1383,212 +1383,212 @@
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
         <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:04</t>
+          <t>2026-06-08 17:10:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -875,7 +875,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -896,7 +896,7 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
         <v>2.44</v>
@@ -1380,7 +1380,7 @@
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1548,7 +1548,7 @@
         <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>17.5</v>
@@ -1566,7 +1566,7 @@
         <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BV4" t="n">
         <v>29</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:10:08</t>
+          <t>2026-06-08 19:17:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
         <v>3.95</v>
@@ -908,7 +908,7 @@
         <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
@@ -971,10 +971,10 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
@@ -1007,16 +1007,16 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BN3" t="n">
         <v>5.9</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1392,10 +1392,10 @@
         <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
         <v>2.04</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1637,16 +1637,16 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.83</v>
@@ -1655,194 +1655,194 @@
         <v>2.06</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
@@ -1891,212 +1891,974 @@
         <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
         <v>2.68</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>990</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-08 21:25:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-08 21:25:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>SK Kladno</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="CA3" t="n">
         <v>7.6</v>
       </c>
-      <c r="BG3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU4" t="n">
         <v>1.69</v>
       </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5</v>
-      </c>
       <c r="BV4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.4</v>
+        <v>1.91</v>
       </c>
       <c r="BX4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>1.91</v>
       </c>
       <c r="BZ4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.4</v>
+        <v>1.83</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
         <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>55</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BG5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV5" t="n">
         <v>29</v>
       </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW5" t="n">
-        <v>1.74</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.75</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.71</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>2.26</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>2.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>1.96</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>2.08</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>2.32</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>2.14</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>2.14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>2.32</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="BB6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>34</v>
-      </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="BP6" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
         <v>5.7</v>
       </c>
-      <c r="I7" t="n">
-        <v>990</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>2.36</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,493 +2372,747 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 21:25:11</t>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-08 23:32:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Inter Toronto FC</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Cavalry</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="F10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.98</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>1.33</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-08 21:25:11</t>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-08 23:32:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
         <v>3.95</v>
@@ -1123,10 +1123,10 @@
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1150,19 +1150,19 @@
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
@@ -1183,7 +1183,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
@@ -1198,7 +1198,7 @@
         <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -1207,13 +1207,13 @@
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
         <v>60</v>
@@ -1225,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>7.2</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
         <v>18.5</v>
@@ -1261,34 +1261,34 @@
         <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
@@ -1300,13 +1300,13 @@
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
         <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
         <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -1380,13 +1380,13 @@
         <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>4.1</v>
@@ -1395,19 +1395,19 @@
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.76</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>2.08</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
         <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1640,37 +1640,37 @@
         <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
         <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
         <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U5" t="n">
         <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1694,13 +1694,13 @@
         <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>18.5</v>
@@ -1709,7 +1709,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1721,22 +1721,22 @@
         <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>8.6</v>
@@ -1763,7 +1763,7 @@
         <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
         <v>18.5</v>
@@ -1772,10 +1772,10 @@
         <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG5" t="n">
         <v>30</v>
@@ -1784,7 +1784,7 @@
         <v>3.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.800000000000001</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
         <v>5.2</v>
@@ -1805,7 +1805,7 @@
         <v>3.95</v>
       </c>
       <c r="BP5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5" t="n">
         <v>7.6</v>
@@ -1826,30 +1826,30 @@
         <v>29</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>42</v>
       </c>
       <c r="BY5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>1.86</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.76</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.08</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>1.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,72 +2367,72 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>9.4</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,72 +2546,72 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.24</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>1.03</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 23:32:26</t>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,33 +2875,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2913,206 +2913,2492 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kari</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Selfoss</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KFG</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hviti Riddarinn</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Haukar</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kormakur/Hvot</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>950</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>990</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
         <v>2.98</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X17" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.32</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P18" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q18" t="n">
         <v>1.96</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R18" t="n">
         <v>1.25</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T18" t="n">
         <v>1.11</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U18" t="n">
         <v>1.11</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="V18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.2</v>
       </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
         <v>4.1</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BI18" t="n">
         <v>2.44</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>1.33</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
         <v>1.33</v>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-08 23:32:26</t>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:40:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,7 +872,7 @@
         <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1141,13 +1141,13 @@
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
@@ -1156,13 +1156,13 @@
         <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
         <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
@@ -1183,7 +1183,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
@@ -1192,7 +1192,7 @@
         <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>19</v>
@@ -1213,7 +1213,7 @@
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO3" t="n">
         <v>60</v>
@@ -1225,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>7.2</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
         <v>18.5</v>
@@ -1261,16 +1261,16 @@
         <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
@@ -1279,19 +1279,19 @@
         <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
         <v>3.8</v>
@@ -1300,16 +1300,16 @@
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3" t="n">
         <v>5.8</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -1383,31 +1383,31 @@
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>2.08</v>
@@ -1416,10 +1416,10 @@
         <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>21</v>
@@ -1455,10 +1455,10 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
@@ -1479,10 +1479,10 @@
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>7.6</v>
@@ -1494,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX4" t="n">
         <v>8.800000000000001</v>
@@ -1506,7 +1506,7 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
         <v>13.5</v>
@@ -1515,7 +1515,7 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
         <v>6</v>
@@ -1524,71 +1524,71 @@
         <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.72</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.97</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="BP4" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.75</v>
+        <v>5.3</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.86</v>
+        <v>7</v>
       </c>
       <c r="BT4" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.69</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.91</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.91</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.83</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
         <v>2.42</v>
@@ -1628,13 +1628,13 @@
         <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>1.35</v>
@@ -1649,7 +1649,7 @@
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
         <v>2.06</v>
@@ -1658,7 +1658,7 @@
         <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
         <v>1.81</v>
@@ -1667,7 +1667,7 @@
         <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
         <v>1.7</v>
@@ -1712,7 +1712,7 @@
         <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
@@ -1724,7 +1724,7 @@
         <v>22</v>
       </c>
       <c r="AO5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
         <v>11.5</v>
@@ -1769,7 +1769,7 @@
         <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
         <v>9.800000000000001</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -1885,10 +1885,10 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -2139,10 +2139,10 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2420,7 +2420,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2650,7 +2650,7 @@
         <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2901,10 +2901,10 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3134,22 +3134,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3412,7 +3412,7 @@
         <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3424,19 +3424,19 @@
         <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3678,19 +3678,19 @@
         <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.07</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
         <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.56</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.56</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG15" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL15" t="n">
         <v>40</v>
       </c>
-      <c r="AK15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>65</v>
-      </c>
       <c r="AM15" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU15" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY15" t="n">
         <v>9</v>
       </c>
-      <c r="AX15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BE15" t="n">
         <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>11</v>
-      </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA15" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73</v>
+        <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS16" t="n">
         <v>9.4</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="G17" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="H17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.85</v>
       </c>
-      <c r="I17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.29</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>410</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
         <v>40</v>
       </c>
-      <c r="AA17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>21</v>
-      </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV17" t="n">
+      <c r="BK17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BT17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>8</v>
-      </c>
       <c r="BU17" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.4</v>
+        <v>1.61</v>
       </c>
       <c r="BZ17" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,498 +4907,752 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO18" t="n">
         <v>3.7</v>
       </c>
-      <c r="G18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.33</v>
+        <v>5.8</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.33</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:49:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>1.73</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="G20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H20" t="n">
         <v>5.2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>6.6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>3.45</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L20" t="n">
         <v>1.4</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M20" t="n">
         <v>1.09</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O20" t="n">
         <v>1.41</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P20" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="Q20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.25</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>4.3</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="T20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.8</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V20" t="n">
         <v>1.17</v>
       </c>
-      <c r="W19" t="n">
+      <c r="W20" t="n">
         <v>1.93</v>
       </c>
-      <c r="X19" t="n">
+      <c r="X20" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y20" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z20" t="n">
         <v>44</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA20" t="n">
         <v>180</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AB20" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AC20" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD20" t="n">
         <v>23</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AE20" t="n">
         <v>110</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AF20" t="n">
         <v>11</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AH20" t="n">
         <v>25</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AI20" t="n">
         <v>120</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AJ20" t="n">
         <v>22</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK20" t="n">
         <v>24</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL20" t="n">
         <v>48</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AM20" t="n">
         <v>190</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AN20" t="n">
         <v>19.5</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AO20" t="n">
         <v>150</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AP20" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ20" t="n">
         <v>11</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR20" t="n">
         <v>29</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AS20" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AT20" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AU20" t="n">
         <v>7</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AV20" t="n">
         <v>18</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AW20" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AX20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AY20" t="n">
         <v>9</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="AZ20" t="n">
         <v>19</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BA20" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB20" t="n">
         <v>17</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BC20" t="n">
         <v>19</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BD20" t="n">
         <v>38</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BE20" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BF20" t="n">
         <v>12</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BG20" t="n">
         <v>6.6</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BH20" t="n">
         <v>3.15</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BI20" t="n">
         <v>2.46</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BJ20" t="n">
         <v>12</v>
       </c>
-      <c r="BK19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN19" t="n">
+      <c r="BK20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN20" t="n">
         <v>4.4</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BO20" t="n">
         <v>3.3</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BP20" t="n">
         <v>14</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BQ20" t="n">
         <v>5.9</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="BR20" t="n">
         <v>36</v>
       </c>
-      <c r="BS19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT19" t="n">
+      <c r="BS20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="BU20" t="n">
         <v>4.8</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="BV20" t="n">
         <v>60</v>
       </c>
-      <c r="BW19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY19" t="n">
+      <c r="BW20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY20" t="n">
         <v>9</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="BZ20" t="n">
         <v>32</v>
       </c>
-      <c r="CA19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>2026-06-09 01:40:50</t>
+      <c r="CA20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1147,7 +1147,7 @@
         <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
@@ -1159,118 +1159,118 @@
         <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP3" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>12</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
@@ -1282,7 +1282,7 @@
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.3</v>
@@ -1389,10 +1389,10 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
@@ -1404,19 +1404,19 @@
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1449,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>75</v>
@@ -1479,10 +1479,10 @@
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
         <v>7.6</v>
@@ -1494,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>8.800000000000001</v>
@@ -1515,19 +1515,19 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
         <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
         <v>5.9</v>
       </c>
       <c r="BH4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI4" t="n">
         <v>3.15</v>
@@ -1545,16 +1545,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR4" t="n">
         <v>25</v>
@@ -1563,32 +1563,32 @@
         <v>7</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA4" t="n">
         <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
@@ -1643,19 +1643,19 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
         <v>3.75</v>
@@ -1667,31 +1667,31 @@
         <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
         <v>42</v>
@@ -1736,10 +1736,10 @@
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1751,28 +1751,28 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
         <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
         <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
@@ -1781,22 +1781,22 @@
         <v>30</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5.2</v>
@@ -1805,44 +1805,44 @@
         <v>3.95</v>
       </c>
       <c r="BP5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>29</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1897,10 +1897,10 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
@@ -1912,7 +1912,7 @@
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,28 +2626,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,19 +2659,19 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
         <v>1.01</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,22 +2880,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
         <v>1.02</v>
@@ -3170,19 +3170,19 @@
         <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>Vikingur Olafsvik</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3917,10 +3917,10 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,244 +4145,244 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.19</v>
       </c>
-      <c r="S16" t="n">
+      <c r="W16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>5.6</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AX16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ16" t="n">
+      <c r="BK16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT16" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA16" t="n">
+      <c r="BU16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="CA16" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>12</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="G17" t="n">
-        <v>1.58</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>11.5</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN17" t="n">
         <v>5.2</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>410</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="BO17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
         <v>12</v>
       </c>
-      <c r="AH17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.85</v>
       </c>
-      <c r="I18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>410</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB18" t="n">
         <v>3.9</v>
       </c>
-      <c r="K18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="X18" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ18" t="n">
+      <c r="BC18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ18" t="n">
+      <c r="BK18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BT18" t="n">
         <v>12.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>8</v>
-      </c>
       <c r="BU18" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>1.61</v>
       </c>
       <c r="BZ18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,498 +5161,752 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="G19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X19" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK19" t="n">
         <v>5.1</v>
       </c>
-      <c r="H19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X19" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR19" t="n">
         <v>26</v>
       </c>
-      <c r="AF19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cavalry</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-09 05:57:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.9</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>5.2</v>
       </c>
-      <c r="I20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="I21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.45</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>3.85</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>1.4</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>1.09</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="O21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.26</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
         <v>4.3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2.06</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>1.8</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="V21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.93</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X21" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="Y21" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO21" t="n">
         <v>180</v>
       </c>
-      <c r="AB20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AP21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY20" t="n">
+      <c r="BX21" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY21" t="n">
         <v>9</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ20" t="n">
+      <c r="BZ21" t="n">
         <v>32</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CA21" t="n">
         <v>7.6</v>
       </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-06-09 03:49:16</t>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
         <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>4.5</v>
@@ -1126,7 +1126,7 @@
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1141,10 +1141,10 @@
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
@@ -1168,19 +1168,19 @@
         <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
         <v>19.5</v>
@@ -1189,7 +1189,7 @@
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
@@ -1198,49 +1198,49 @@
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
         <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.5</v>
+        <v>44</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,25 +1252,25 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
       </c>
       <c r="BD3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG3" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
@@ -1282,7 +1282,7 @@
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.3</v>
@@ -1389,31 +1389,31 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
         <v>2.22</v>
@@ -1449,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
         <v>75</v>
@@ -1458,10 +1458,10 @@
         <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -1473,40 +1473,40 @@
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>13.5</v>
@@ -1515,22 +1515,22 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1649,22 +1649,22 @@
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
@@ -1673,7 +1673,7 @@
         <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
@@ -1718,7 +1718,7 @@
         <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
         <v>22</v>
@@ -1730,55 +1730,55 @@
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
         <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
         <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BF5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
         <v>3.3</v>
@@ -1820,7 +1820,7 @@
         <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
         <v>28</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -1897,10 +1897,10 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
@@ -1912,7 +1912,7 @@
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P9" t="n">
         <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
         <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P10" t="n">
         <v>1.07</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P11" t="n">
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -4422,16 +4422,16 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -4461,7 +4461,7 @@
         <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
         <v>2.16</v>
@@ -4473,7 +4473,7 @@
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
         <v>170</v>
@@ -4491,10 +4491,10 @@
         <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
         <v>26</v>
@@ -4509,28 +4509,28 @@
         <v>24</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
         <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO16" t="n">
         <v>120</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>30</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
         <v>7.2</v>
@@ -4539,10 +4539,10 @@
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
         <v>9.4</v>
@@ -4554,25 +4554,25 @@
         <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="n">
         <v>3.35</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
         <v>3.75</v>
@@ -4685,22 +4685,22 @@
         <v>3.15</v>
       </c>
       <c r="L17" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
         <v>1.19</v>
@@ -4709,16 +4709,16 @@
         <v>5.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
         <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X17" t="n">
         <v>10.5</v>
@@ -4733,10 +4733,10 @@
         <v>95</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>19.5</v>
@@ -4748,10 +4748,10 @@
         <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
         <v>100</v>
@@ -4775,16 +4775,16 @@
         <v>100</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
@@ -4793,40 +4793,40 @@
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="AY17" t="n">
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF17" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF17" t="n">
-        <v>4</v>
-      </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH17" t="n">
         <v>2.7</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G18" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I18" t="n">
         <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
         <v>5.2</v>
@@ -4945,7 +4945,7 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
         <v>1.29</v>
@@ -4960,7 +4960,7 @@
         <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T18" t="n">
         <v>2.08</v>
@@ -4972,7 +4972,7 @@
         <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="X18" t="n">
         <v>18.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -5175,70 +5175,70 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
         <v>1.68</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
         <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
         <v>13</v>
@@ -5253,22 +5253,22 @@
         <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>38</v>
@@ -5277,70 +5277,70 @@
         <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO19" t="n">
         <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
@@ -5352,53 +5352,53 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
         <v>7.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA19" t="n">
         <v>7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -5429,58 +5429,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H20" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="I20" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
         <v>1.96</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
         <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5489,10 +5489,10 @@
         <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB20" t="n">
         <v>950</v>
@@ -5504,10 +5504,10 @@
         <v>950</v>
       </c>
       <c r="AE20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG20" t="n">
         <v>950</v>
@@ -5522,7 +5522,7 @@
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -5534,7 +5534,7 @@
         <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AP20" t="n">
         <v>3.9</v>
@@ -5543,25 +5543,25 @@
         <v>3.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW20" t="n">
         <v>4.3</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY20" t="n">
         <v>4.1</v>
@@ -5573,34 +5573,34 @@
         <v>4.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="BC20" t="n">
         <v>4.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,7 +5612,7 @@
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5624,35 +5624,35 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G21" t="n">
         <v>1.9</v>
@@ -5713,19 +5713,19 @@
         <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
         <v>2.26</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
         <v>1.8</v>
@@ -5749,10 +5749,10 @@
         <v>210</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>28</v>
@@ -5791,31 +5791,31 @@
         <v>180</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11</v>
       </c>
       <c r="AR21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS21" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS21" t="n">
-        <v>5</v>
-      </c>
       <c r="AT21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
@@ -5824,25 +5824,25 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC21" t="n">
         <v>18.5</v>
       </c>
       <c r="BD21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE21" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE21" t="n">
-        <v>5</v>
-      </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="n">
         <v>3.15</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.88</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.2</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1135,88 +1135,88 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
         <v>11</v>
@@ -1225,13 +1225,13 @@
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS3" t="n">
         <v>5</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
@@ -1240,101 +1240,101 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>44</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA3" t="n">
         <v>10</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>27</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1365,76 +1365,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.76</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
         <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
         <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>23</v>
@@ -1479,10 +1479,10 @@
         <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1494,7 +1494,7 @@
         <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1506,7 +1506,7 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>13.5</v>
@@ -1515,19 +1515,19 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
         <v>3.1</v>
@@ -1536,16 +1536,16 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
         <v>3.6</v>
@@ -1554,41 +1554,41 @@
         <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -1622,55 +1622,55 @@
         <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
         <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
         <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1679,7 +1679,7 @@
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
         <v>65</v>
@@ -1688,10 +1688,10 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>42</v>
@@ -1700,10 +1700,10 @@
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1712,16 +1712,16 @@
         <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
         <v>42</v>
@@ -1730,25 +1730,25 @@
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
         <v>13</v>
@@ -1760,25 +1760,25 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BB5" t="n">
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>70</v>
+        <v>14.5</v>
       </c>
       <c r="BF5" t="n">
         <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH5" t="n">
         <v>3.3</v>
@@ -1820,7 +1820,7 @@
         <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV5" t="n">
         <v>28</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
-        <v>110</v>
+        <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>110</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.25</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q12" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O13" t="n">
         <v>1.07</v>
@@ -3699,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
         <v>1.14</v>
@@ -3953,10 +3953,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -4413,49 +4413,49 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U16" t="n">
         <v>1.94</v>
@@ -4464,10 +4464,10 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
         <v>21</v>
@@ -4476,22 +4476,22 @@
         <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4518,125 +4518,125 @@
         <v>15.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>4.1</v>
       </c>
       <c r="AW16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BE16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
         <v>2.48</v>
@@ -4676,7 +4676,7 @@
         <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -4688,10 +4688,10 @@
         <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
@@ -4700,94 +4700,94 @@
         <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
         <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y17" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>12</v>
-      </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL17" t="n">
         <v>95</v>
       </c>
-      <c r="AB17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>80</v>
-      </c>
       <c r="AM17" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -4796,40 +4796,40 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.75</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI17" t="n">
         <v>2.3</v>
@@ -4838,13 +4838,13 @@
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN17" t="n">
         <v>5.2</v>
@@ -4856,13 +4856,13 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT17" t="n">
         <v>6.6</v>
@@ -4880,17 +4880,17 @@
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
         <v>12.5</v>
       </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>12</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>1.42</v>
       </c>
       <c r="G18" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
         <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>5.2</v>
@@ -4960,7 +4960,7 @@
         <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
         <v>2.08</v>
@@ -4972,7 +4972,7 @@
         <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="X18" t="n">
         <v>18.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>3.9</v>
@@ -5193,160 +5193,160 @@
         <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.24</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.26</v>
-      </c>
       <c r="W19" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA19" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
         <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
         <v>12.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC19" t="n">
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE19" t="n">
         <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG19" t="n">
         <v>4</v>
       </c>
       <c r="BH19" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,10 +5355,10 @@
         <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP19" t="n">
         <v>12.5</v>
@@ -5367,38 +5367,38 @@
         <v>5.9</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CA19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.37</v>
@@ -5453,16 +5453,16 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.34</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1.3</v>
@@ -5471,16 +5471,16 @@
         <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
         <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5489,10 +5489,10 @@
         <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="n">
         <v>950</v>
@@ -5504,10 +5504,10 @@
         <v>950</v>
       </c>
       <c r="AE20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
         <v>950</v>
@@ -5516,13 +5516,13 @@
         <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ20" t="n">
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -5534,73 +5534,73 @@
         <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>2.82</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="BE20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
         <v>2.7</v>
       </c>
-      <c r="BF20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.72</v>
-      </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,7 +5612,7 @@
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5624,13 +5624,13 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5642,17 +5642,17 @@
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -5710,203 +5710,203 @@
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V21" t="n">
         <v>1.16</v>
       </c>
       <c r="W21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD21" t="n">
         <v>1.93</v>
       </c>
-      <c r="X21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="BE21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BF21" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BR21" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.8</v>
+        <v>1.37</v>
       </c>
       <c r="BT21" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>8.6</v>
+        <v>1.38</v>
       </c>
       <c r="BX21" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="CA21" t="n">
-        <v>7.6</v>
+        <v>1.36</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,175 +857,175 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.88</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
         <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
         <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
         <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
@@ -1037,13 +1037,13 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.01</v>
@@ -1055,13 +1055,13 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
         <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW2" t="n">
         <v>1.01</v>
@@ -1073,14 +1073,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA2" t="n">
         <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -1135,10 +1135,10 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
         <v>1.9</v>
@@ -1147,7 +1147,7 @@
         <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
@@ -1156,16 +1156,16 @@
         <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
         <v>15</v>
@@ -1183,13 +1183,13 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1210,7 +1210,7 @@
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
         <v>16.5</v>
@@ -1225,10 +1225,10 @@
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>8.199999999999999</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1252,25 +1252,25 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1294,7 +1294,7 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
@@ -1312,7 +1312,7 @@
         <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>34</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
         <v>1.83</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1395,19 +1395,19 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
         <v>2.1</v>
@@ -1416,10 +1416,10 @@
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>21</v>
@@ -1473,16 +1473,16 @@
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
         <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1494,7 +1494,7 @@
         <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
         <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
         <v>3.75</v>
@@ -1667,13 +1667,13 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.72</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
@@ -1685,7 +1685,7 @@
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1694,16 +1694,16 @@
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1712,22 +1712,22 @@
         <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
         <v>42</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>11.5</v>
@@ -1742,7 +1742,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
@@ -1754,7 +1754,7 @@
         <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
         <v>16.5</v>
@@ -1772,13 +1772,13 @@
         <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG5" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.3</v>
@@ -1790,7 +1790,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>17.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
@@ -1820,7 +1820,7 @@
         <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>28</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.21</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
@@ -1900,85 +1900,85 @@
         <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP6" t="n">
         <v>1.03</v>
@@ -1993,10 +1993,10 @@
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
         <v>1.03</v>
@@ -2005,43 +2005,43 @@
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BG6" t="n">
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BI6" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,25 +2053,25 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
@@ -2089,14 +2089,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.55</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>5.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.26</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="R7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>1.24</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -2381,237 +2381,237 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
         <v>13</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="CA8" t="n">
         <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,127 +2626,127 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
         <v>1.03</v>
@@ -2755,37 +2755,37 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
         <v>1.03</v>
@@ -2797,75 +2797,75 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>2.94</v>
       </c>
       <c r="J10" t="n">
-        <v>1.92</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,136 +2913,136 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>2.62</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -3143,160 +3143,160 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="G11" t="n">
-        <v>5.6</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="J12" t="n">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.07</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3559,13 +3559,13 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI12" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK12" t="n">
         <v>1.01</v>
@@ -3577,13 +3577,13 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO12" t="n">
         <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.01</v>
@@ -3595,19 +3595,19 @@
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
         <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW12" t="n">
         <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BY12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -3651,160 +3651,160 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="S13" t="n">
-        <v>1.06</v>
+        <v>1.77</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>1.96</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
         <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3813,13 +3813,13 @@
         <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI13" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK13" t="n">
         <v>1.01</v>
@@ -3831,7 +3831,7 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO13" t="n">
         <v>1.01</v>
@@ -3849,32 +3849,32 @@
         <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU13" t="n">
         <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
         <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY13" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA13" t="n">
         <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -3905,160 +3905,160 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>2.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>1.14</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -4159,52 +4159,52 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="J15" t="n">
-        <v>1.96</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
         <v>6.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -4213,103 +4213,103 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
         <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
         <v>1.03</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
@@ -4431,7 +4431,7 @@
         <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -4464,7 +4464,7 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
@@ -4473,7 +4473,7 @@
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="n">
         <v>180</v>
@@ -4482,7 +4482,7 @@
         <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
         <v>26</v>
@@ -4491,7 +4491,7 @@
         <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4506,7 +4506,7 @@
         <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
         <v>48</v>
@@ -4521,58 +4521,58 @@
         <v>130</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH16" t="n">
         <v>3.3</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -4685,10 +4685,10 @@
         <v>3.15</v>
       </c>
       <c r="L17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N17" t="n">
         <v>2.72</v>
@@ -4706,13 +4706,13 @@
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
@@ -4730,7 +4730,7 @@
         <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
         <v>7.4</v>
@@ -4742,7 +4742,7 @@
         <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
         <v>970</v>
@@ -4754,25 +4754,25 @@
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN17" t="n">
         <v>40</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
         <v>7.8</v>
@@ -4781,10 +4781,10 @@
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4796,7 +4796,7 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -4805,46 +4805,46 @@
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ17" t="n">
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN17" t="n">
         <v>5.2</v>
@@ -4853,10 +4853,10 @@
         <v>3.95</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4880,7 +4880,7 @@
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
@@ -4927,13 +4927,13 @@
         <v>1.56</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="I18" t="n">
         <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
         <v>5.2</v>
@@ -4945,7 +4945,7 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
         <v>1.29</v>
@@ -4960,7 +4960,7 @@
         <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
         <v>2.08</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,246 +5166,246 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Fort Wayne FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="G19" t="n">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>2.02</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>2.58</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>2.08</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AC19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BZ19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="G20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K20" t="n">
         <v>4.5</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA20" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.32</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.74</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.52</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.26</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.42</v>
+        <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.64</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.86</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.07</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.91</v>
+        <v>3.55</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,244 +5669,498 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>3.35</v>
       </c>
       <c r="G21" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>2.02</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>2.32</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>950</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AD21" t="n">
         <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AG21" t="n">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AH21" t="n">
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL21" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:24:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK22" t="n">
         <v>24</v>
       </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AL22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>44</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:15:48</t>
+      <c r="BN22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G2" t="n">
         <v>2.54</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
         <v>3.6</v>
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -890,7 +890,7 @@
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -899,7 +899,7 @@
         <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
         <v>2.2</v>
@@ -965,58 +965,58 @@
         <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.9</v>
@@ -1028,59 +1028,59 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV2" t="n">
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
         <v>24</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1141,10 +1141,10 @@
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -1159,118 +1159,118 @@
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX3" t="n">
         <v>11</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1294,13 +1294,13 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.74</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
@@ -1398,10 +1398,10 @@
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1410,13 +1410,13 @@
         <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
         <v>19</v>
@@ -1425,7 +1425,7 @@
         <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>140</v>
@@ -1434,13 +1434,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
@@ -1449,10 +1449,10 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>20</v>
@@ -1479,10 +1479,10 @@
         <v>15.5</v>
       </c>
       <c r="AR4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS4" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1491,10 +1491,10 @@
         <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1506,7 +1506,7 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
         <v>13.5</v>
@@ -1515,22 +1515,22 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.65</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X5" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU5" t="n">
         <v>3.75</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV5" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="AZ5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP5" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BV5" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC6" t="n">
         <v>23</v>
       </c>
-      <c r="J6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>140</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>260</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="BD6" t="n">
         <v>36</v>
       </c>
-      <c r="AD6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.81</v>
+        <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>20</v>
-      </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>1.21</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>13.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>23</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>5.3</v>
       </c>
       <c r="X7" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Y7" t="n">
+        <v>140</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>260</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
         <v>34</v>
       </c>
-      <c r="Z7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>32</v>
-      </c>
       <c r="AC7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>16</v>
       </c>
-      <c r="AD7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AK7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR7" t="n">
         <v>16</v>
       </c>
-      <c r="AH7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS7" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BU7" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.99</v>
+        <v>3.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UMF Tindstoll</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>2.66</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>1.07</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BX8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
         <v>5.5</v>
@@ -2671,10 +2671,10 @@
         <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="T9" t="n">
         <v>1.44</v>
@@ -2692,109 +2692,109 @@
         <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN9" t="n">
         <v>5.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH9" t="n">
         <v>6.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -2880,169 +2880,169 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.94</v>
+        <v>7.6</v>
       </c>
       <c r="J10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R10" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="T10" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3051,68 +3051,68 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -3134,34 +3134,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KFA Austfjarda</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -3170,88 +3170,88 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z11" t="n">
         <v>34</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM11" t="n">
         <v>36</v>
       </c>
-      <c r="AA11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>42</v>
-      </c>
       <c r="AN11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.01</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>6.6</v>
       </c>
-      <c r="BI11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP11" t="n">
+      <c r="BR11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX11" t="n">
         <v>17</v>
       </c>
-      <c r="BQ11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>20</v>
-      </c>
       <c r="BY11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74</v>
+        <v>2.06</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="R12" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="W12" t="n">
         <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BH12" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>8.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>Vikingur Olafsvik</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.04</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="U13" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.96</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK13" t="n">
         <v>21</v>
       </c>
-      <c r="AF13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>38</v>
-      </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AO13" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT13" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -3896,34 +3896,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vikingur Olafsvik</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3932,210 +3932,210 @@
         <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="AB14" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="AL14" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,39 +4145,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K15" t="n">
         <v>5.4</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.6</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -4186,203 +4186,203 @@
         <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="T15" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
         <v>29</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>21</v>
       </c>
       <c r="AF15" t="n">
         <v>40</v>
       </c>
       <c r="AG15" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM15" t="n">
         <v>32</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -4464,7 +4464,7 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
@@ -4569,7 +4569,7 @@
         <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
         <v>4.3</v>
@@ -4584,7 +4584,7 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR16" t="n">
         <v>30</v>
@@ -4614,7 +4614,7 @@
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
         <v>2.48</v>
@@ -4676,7 +4676,7 @@
         <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -4691,13 +4691,13 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>2.64</v>
@@ -4718,40 +4718,40 @@
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
         <v>110</v>
@@ -4760,7 +4760,7 @@
         <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL17" t="n">
         <v>65</v>
@@ -4781,10 +4781,10 @@
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4796,7 +4796,7 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -4805,28 +4805,28 @@
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
         <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BG17" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="n">
         <v>2.66</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -4921,61 +4921,61 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
         <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
         <v>1.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
         <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
         <v>32</v>
@@ -4984,10 +4984,10 @@
         <v>95</v>
       </c>
       <c r="AA18" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>12.5</v>
@@ -5017,134 +5017,134 @@
         <v>19</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>9</v>
       </c>
       <c r="AO18" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AW18" t="n">
         <v>5.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE18" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF18" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.56</v>
+        <v>10.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BZ18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -5178,16 +5178,16 @@
         <v>2.78</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="I19" t="n">
         <v>2.58</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
         <v>4.7</v>
@@ -5199,7 +5199,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
@@ -5208,7 +5208,7 @@
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="R19" t="n">
         <v>1.45</v>
@@ -5346,49 +5346,49 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -5429,31 +5429,31 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.26</v>
@@ -5462,37 +5462,37 @@
         <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U20" t="n">
         <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
         <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
@@ -5504,10 +5504,10 @@
         <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -5519,10 +5519,10 @@
         <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>40</v>
@@ -5540,10 +5540,10 @@
         <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS20" t="n">
         <v>4.1</v>
@@ -5552,16 +5552,16 @@
         <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
         <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
@@ -5573,10 +5573,10 @@
         <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>3.85</v>
@@ -5585,7 +5585,7 @@
         <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
         <v>4</v>
@@ -5594,7 +5594,7 @@
         <v>3.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
@@ -5612,13 +5612,13 @@
         <v>4.7</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR20" t="n">
         <v>26</v>
@@ -5627,7 +5627,7 @@
         <v>7.8</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
         <v>4.9</v>
@@ -5642,17 +5642,17 @@
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -5689,49 +5689,49 @@
         <v>4.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
         <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T21" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.98</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
         <v>1.3</v>
@@ -5770,7 +5770,7 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -5797,19 +5797,19 @@
         <v>3.45</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS21" t="n">
         <v>4.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AW21" t="n">
         <v>4.3</v>
@@ -5821,64 +5821,64 @@
         <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
         <v>4.7</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
@@ -5890,7 +5890,7 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>
@@ -5940,19 +5940,19 @@
         <v>1.81</v>
       </c>
       <c r="G22" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
         <v>5.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.39</v>
@@ -5967,16 +5967,16 @@
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
         <v>2.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
         <v>2.06</v>
@@ -5991,25 +5991,25 @@
         <v>1.91</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
         <v>200</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
         <v>110</v>
@@ -6018,10 +6018,10 @@
         <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
         <v>120</v>
@@ -6033,13 +6033,13 @@
         <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>170</v>
@@ -6051,10 +6051,10 @@
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AT22" t="n">
         <v>6.4</v>
@@ -6063,10 +6063,10 @@
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -6078,7 +6078,7 @@
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6090,13 +6090,13 @@
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BH22" t="n">
         <v>3.15</v>
@@ -6120,7 +6120,7 @@
         <v>4.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP22" t="n">
         <v>14</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -869,7 +869,7 @@
         <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -878,25 +878,25 @@
         <v>1.34</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="P2" t="n">
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
@@ -935,7 +935,7 @@
         <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -944,7 +944,7 @@
         <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
         <v>36</v>
@@ -968,7 +968,7 @@
         <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
         <v>4.3</v>
@@ -977,13 +977,13 @@
         <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW2" t="n">
         <v>4.5</v>
@@ -992,7 +992,7 @@
         <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -1111,28 +1111,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
         <v>3.6</v>
@@ -1141,10 +1141,10 @@
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -1159,13 +1159,13 @@
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
         <v>16</v>
@@ -1177,7 +1177,7 @@
         <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
@@ -1192,19 +1192,19 @@
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>38</v>
@@ -1222,13 +1222,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1237,10 +1237,10 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1252,7 +1252,7 @@
         <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1261,16 +1261,16 @@
         <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1300,7 +1300,7 @@
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
         <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
         <v>19</v>
@@ -1428,16 +1428,16 @@
         <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
@@ -1449,10 +1449,10 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
         <v>20</v>
@@ -1467,10 +1467,10 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
@@ -1482,7 +1482,7 @@
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1494,7 +1494,7 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1506,7 +1506,7 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>13.5</v>
@@ -1515,16 +1515,16 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
@@ -1536,7 +1536,7 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1560,22 +1560,22 @@
         <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV4" t="n">
         <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>8.6</v>
@@ -1584,11 +1584,11 @@
         <v>20</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -1643,10 +1643,10 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P5" t="n">
         <v>4.2</v>
@@ -1673,7 +1673,7 @@
         <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.3</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.36</v>
-      </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
         <v>1.34</v>
@@ -1915,178 +1915,178 @@
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF6" t="n">
         <v>14</v>
       </c>
-      <c r="AE6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK6" t="n">
         <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BH6" t="n">
         <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
         <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
         <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>28</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>29</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="H7" t="n">
         <v>13.5</v>
       </c>
       <c r="I7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>1.05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q7" t="n">
         <v>1.15</v>
@@ -2166,7 +2166,7 @@
         <v>2.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
         <v>1.67</v>
@@ -2175,16 +2175,16 @@
         <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
         <v>5.3</v>
       </c>
       <c r="X7" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>260</v>
@@ -2199,7 +2199,7 @@
         <v>36</v>
       </c>
       <c r="AD7" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
         <v>240</v>
@@ -2235,10 +2235,10 @@
         <v>150</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.62</v>
+        <v>5.1</v>
       </c>
       <c r="AR7" t="n">
         <v>1.63</v>
@@ -2256,7 +2256,7 @@
         <v>4.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.63</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
         <v>4.1</v>
@@ -2268,7 +2268,7 @@
         <v>4.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.62</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
         <v>3.95</v>
@@ -2280,13 +2280,13 @@
         <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
         <v>1.81</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.62</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
         <v>8.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
         <v>2.46</v>
@@ -2402,7 +2402,7 @@
         <v>1.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
         <v>1.1</v>
@@ -2420,7 +2420,7 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="T8" t="n">
         <v>1.33</v>
@@ -2435,10 +2435,10 @@
         <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>36</v>
@@ -2447,7 +2447,7 @@
         <v>50</v>
       </c>
       <c r="AB8" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AC8" t="n">
         <v>970</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
         <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
         <v>5.5</v>
@@ -2662,7 +2662,7 @@
         <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -2671,16 +2671,16 @@
         <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="T9" t="n">
         <v>1.44</v>
       </c>
       <c r="U9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2689,10 +2689,10 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>60</v>
@@ -2701,13 +2701,13 @@
         <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>55</v>
@@ -2797,68 +2797,68 @@
         <v>3.85</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.96</v>
+        <v>1.07</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.91</v>
+        <v>1.05</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -2922,10 +2922,10 @@
         <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="R10" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
         <v>1.54</v>
@@ -2943,112 +2943,112 @@
         <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="n">
         <v>7.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="I11" t="n">
         <v>2.4</v>
@@ -3182,13 +3182,13 @@
         <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V11" t="n">
         <v>1.71</v>
@@ -3197,7 +3197,7 @@
         <v>1.48</v>
       </c>
       <c r="X11" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
         <v>38</v>
@@ -3251,58 +3251,58 @@
         <v>7.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
         <v>7.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I12" t="n">
         <v>2.06</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
         <v>5.2</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
@@ -3436,13 +3436,13 @@
         <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V12" t="n">
         <v>1.94</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -3654,22 +3654,22 @@
         <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3702,13 +3702,13 @@
         <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
         <v>38</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
@@ -3959,7 +3959,7 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -3971,7 +3971,7 @@
         <v>26</v>
       </c>
       <c r="AB14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
         <v>970</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.2</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>2.46</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.94</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
@@ -4177,7 +4177,7 @@
         <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -4186,58 +4186,58 @@
         <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P15" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="R15" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
         <v>48</v>
       </c>
       <c r="AA15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF15" t="n">
         <v>60</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>40</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
@@ -4246,143 +4246,143 @@
         <v>970</v>
       </c>
       <c r="AI15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
         <v>26</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>23</v>
-      </c>
       <c r="AM15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="AP15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
         <v>5</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
         <v>4.5</v>
       </c>
-      <c r="BF15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.36</v>
@@ -4443,7 +4443,7 @@
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>2.04</v>
@@ -4464,7 +4464,7 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
@@ -4479,13 +4479,13 @@
         <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>95</v>
@@ -4494,19 +4494,19 @@
         <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>48</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4542,7 +4542,7 @@
         <v>18.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4563,16 +4563,16 @@
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH16" t="n">
         <v>3.3</v>
@@ -4584,7 +4584,7 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>30</v>
@@ -4614,7 +4614,7 @@
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4670,13 @@
         <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -4691,13 +4691,13 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
         <v>2.64</v>
@@ -4718,7 +4718,7 @@
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
         <v>8.800000000000001</v>
@@ -4736,7 +4736,7 @@
         <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>19.5</v>
@@ -4745,7 +4745,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
@@ -4754,10 +4754,10 @@
         <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>44</v>
@@ -4781,10 +4781,10 @@
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4796,101 +4796,101 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.3</v>
+        <v>42</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD17" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD17" t="n">
+      <c r="BE17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF17" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BG17" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.4</v>
       </c>
       <c r="BH17" t="n">
         <v>2.66</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BJ17" t="n">
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT17" t="n">
         <v>6.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -4954,13 +4954,13 @@
         <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
         <v>2.1</v>
@@ -5077,7 +5077,7 @@
         <v>5.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
         <v>5.1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G19" t="n">
         <v>3.7</v>
@@ -5208,13 +5208,13 @@
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
         <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T19" t="n">
         <v>1.54</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -5438,16 +5438,16 @@
         <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5462,19 +5462,19 @@
         <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R20" t="n">
         <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
@@ -5486,10 +5486,10 @@
         <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA20" t="n">
         <v>140</v>
@@ -5546,7 +5546,7 @@
         <v>3.95</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -5558,7 +5558,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX20" t="n">
         <v>8.6</v>
@@ -5570,7 +5570,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
@@ -5579,16 +5579,16 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG20" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4</v>
       </c>
       <c r="BH20" t="n">
         <v>3.85</v>
@@ -5600,16 +5600,16 @@
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO20" t="n">
         <v>3.5</v>
@@ -5618,41 +5618,41 @@
         <v>12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
         <v>4.5</v>
@@ -5701,28 +5701,28 @@
         <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
         <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.15</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.79</v>
@@ -5848,7 +5848,7 @@
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G22" t="n">
         <v>1.82</v>
@@ -5946,13 +5946,13 @@
         <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>1.39</v>
@@ -5964,16 +5964,16 @@
         <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>2.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
@@ -5982,19 +5982,19 @@
         <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V22" t="n">
         <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
         <v>55</v>
@@ -6003,25 +6003,25 @@
         <v>200</v>
       </c>
       <c r="AB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC22" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC22" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
         <v>110</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
         <v>120</v>
@@ -6039,7 +6039,7 @@
         <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>170</v>
@@ -6051,10 +6051,10 @@
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
         <v>6.4</v>
@@ -6066,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -6078,7 +6078,7 @@
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6087,16 +6087,16 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="n">
         <v>3.15</v>
@@ -6120,7 +6120,7 @@
         <v>4.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP22" t="n">
         <v>14</v>
@@ -6147,7 +6147,7 @@
         <v>9.4</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY22" t="n">
         <v>9.800000000000001</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -863,13 +863,13 @@
         <v>2.54</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
         <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -911,7 +911,7 @@
         <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
         <v>16.5</v>
@@ -920,19 +920,19 @@
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
         <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
         <v>18.5</v>
@@ -941,82 +941,82 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
         <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
         <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU2" t="n">
         <v>3.7</v>
       </c>
-      <c r="AU2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AV2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AW2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX2" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX2" t="n">
-        <v>4</v>
-      </c>
       <c r="AY2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="n">
         <v>3.9</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1138,34 +1138,34 @@
         <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
         <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
         <v>16</v>
@@ -1174,13 +1174,13 @@
         <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>19</v>
@@ -1198,61 +1198,61 @@
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>16</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1261,16 +1261,16 @@
         <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1294,13 +1294,13 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
@@ -1312,7 +1312,7 @@
         <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>34</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -1365,169 +1365,169 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.14</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.74</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
         <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU4" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AV4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>17</v>
       </c>
-      <c r="AW4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BB4" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI4" t="n">
         <v>3.05</v>
@@ -1536,59 +1536,59 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
         <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR4" t="n">
         <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
         <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.13</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.24</v>
@@ -1664,22 +1664,22 @@
         <v>1.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
         <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>160</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>50</v>
@@ -1688,7 +1688,7 @@
         <v>36</v>
       </c>
       <c r="AC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD5" t="n">
         <v>18.5</v>
@@ -1697,19 +1697,19 @@
         <v>28</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1718,73 +1718,73 @@
         <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.4</v>
@@ -1802,16 +1802,16 @@
         <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BP5" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS5" t="n">
         <v>5.6</v>
@@ -1832,17 +1832,17 @@
         <v>18.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1897,16 +1897,16 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
         <v>1.34</v>
@@ -1921,10 +1921,10 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1939,16 +1939,16 @@
         <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1966,28 +1966,28 @@
         <v>30</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS6" t="n">
         <v>60</v>
@@ -2002,22 +2002,22 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
@@ -2026,13 +2026,13 @@
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH6" t="n">
         <v>3.3</v>
@@ -2044,25 +2044,25 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
@@ -2071,19 +2071,19 @@
         <v>11</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW6" t="n">
         <v>10.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY6" t="n">
         <v>12</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O7" t="n">
         <v>1.05</v>
@@ -2160,10 +2160,10 @@
         <v>5.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="S7" t="n">
         <v>1.45</v>
@@ -2229,64 +2229,64 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AO7" t="n">
         <v>150</v>
       </c>
       <c r="AP7" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.63</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.64</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
         <v>8.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>5.8</v>
@@ -2405,34 +2405,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
         <v>1.26</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>1.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2441,25 +2441,25 @@
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>950</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
@@ -2468,19 +2468,19 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>970</v>
@@ -2489,64 +2489,64 @@
         <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.85</v>
+        <v>2.46</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AY8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG8" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2564,19 +2564,19 @@
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
         <v>5.1</v>
@@ -2650,37 +2650,37 @@
         <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
         <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="T9" t="n">
         <v>1.44</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2689,112 +2689,112 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW9" t="n">
         <v>20</v>
       </c>
-      <c r="AG9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4</v>
-      </c>
       <c r="AX9" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.48</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2806,34 +2806,34 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.82</v>
+        <v>1.59</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU9" t="n">
         <v>4.9</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
         <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.13</v>
@@ -2913,206 +2913,206 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
         <v>1.54</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U10" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD10" t="n">
         <v>32</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
         <v>24</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>16</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
         <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.8</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.55</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.85</v>
+        <v>14</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BH10" t="n">
         <v>7.8</v>
       </c>
       <c r="BI10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK10" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.3</v>
       </c>
       <c r="BL10" t="n">
         <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BR10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BS10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CA10" t="n">
         <v>5.2</v>
       </c>
-      <c r="BT10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>3.65</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
         <v>5.4</v>
@@ -3167,19 +3167,19 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
         <v>1.07</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S11" t="n">
         <v>1.6</v>
@@ -3194,115 +3194,115 @@
         <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AG11" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ11" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
         <v>27</v>
       </c>
       <c r="AM11" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS11" t="n">
         <v>7.2</v>
       </c>
-      <c r="AP11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AT11" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="BH11" t="n">
         <v>7.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
         <v>3.85</v>
@@ -3421,31 +3421,31 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="R12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="T12" t="n">
         <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W12" t="n">
         <v>1.35</v>
@@ -3454,31 +3454,31 @@
         <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
         <v>17</v>
@@ -3487,76 +3487,76 @@
         <v>25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
         <v>46</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.98</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="n">
         <v>6.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -3672,22 +3672,22 @@
         <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="S13" t="n">
         <v>2.1</v>
@@ -3699,7 +3699,7 @@
         <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.96</v>
@@ -3711,106 +3711,106 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH13" t="n">
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG13" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.2</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H14" t="n">
         <v>1.81</v>
@@ -3917,19 +3917,19 @@
         <v>2.06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.16</v>
@@ -3938,19 +3938,19 @@
         <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
         <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
         <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3968,22 +3968,22 @@
         <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>950</v>
       </c>
       <c r="AC14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE14" t="n">
         <v>970</v>
       </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>21</v>
-      </c>
       <c r="AF14" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,79 +3992,79 @@
         <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU14" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AV14" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4076,7 +4076,7 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4106,7 +4106,7 @@
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.11</v>
@@ -4183,61 +4183,61 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>16</v>
       </c>
       <c r="O15" t="n">
         <v>1.05</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="Q15" t="n">
         <v>1.17</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="U15" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X15" t="n">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AD15" t="n">
         <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
@@ -4246,85 +4246,85 @@
         <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO15" t="n">
         <v>5.9</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG15" t="n">
         <v>4.6</v>
       </c>
-      <c r="AV15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>4.9</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,13 +4336,13 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4354,7 +4354,7 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.06</v>
+        <v>6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H16" t="n">
         <v>5.3</v>
@@ -4428,7 +4428,7 @@
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.36</v>
@@ -4437,7 +4437,7 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
@@ -4458,19 +4458,19 @@
         <v>1.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
         <v>55</v>
@@ -4491,10 +4491,10 @@
         <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>25</v>
@@ -4503,7 +4503,7 @@
         <v>95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4542,7 +4542,7 @@
         <v>18.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4563,19 +4563,19 @@
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI16" t="n">
         <v>2.74</v>
@@ -4584,59 +4584,59 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN16" t="n">
         <v>4.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP16" t="n">
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR16" t="n">
         <v>30</v>
       </c>
       <c r="BS16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>26</v>
       </c>
       <c r="CA16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
         <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
         <v>1.13</v>
@@ -4706,10 +4706,10 @@
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
         <v>1.79</v>
@@ -4745,7 +4745,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
@@ -4769,7 +4769,7 @@
         <v>230</v>
       </c>
       <c r="AN17" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO17" t="n">
         <v>100</v>
@@ -4793,19 +4793,19 @@
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
         <v>42</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
         <v>5.6</v>
@@ -4817,13 +4817,13 @@
         <v>25</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="BG17" t="n">
         <v>5.6</v>
@@ -4868,7 +4868,7 @@
         <v>6.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -4924,58 +4924,58 @@
         <v>1.43</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H18" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J18" t="n">
         <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
         <v>32</v>
@@ -4984,7 +4984,7 @@
         <v>95</v>
       </c>
       <c r="AA18" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="AB18" t="n">
         <v>8.800000000000001</v>
@@ -4999,7 +4999,7 @@
         <v>190</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -5011,10 +5011,10 @@
         <v>160</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
         <v>48</v>
@@ -5026,7 +5026,7 @@
         <v>9</v>
       </c>
       <c r="AO18" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AP18" t="n">
         <v>12.5</v>
@@ -5035,34 +5035,34 @@
         <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX18" t="n">
         <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
         <v>9.6</v>
@@ -5071,25 +5071,25 @@
         <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
         <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK18" t="n">
         <v>7</v>
@@ -5098,16 +5098,16 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.66</v>
+        <v>2.84</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ18" t="n">
         <v>5.9</v>
@@ -5116,10 +5116,10 @@
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU18" t="n">
         <v>7</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.64</v>
+        <v>13</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.64</v>
+        <v>13</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H19" t="n">
         <v>2.16</v>
@@ -5199,22 +5199,22 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
         <v>1.54</v>
@@ -5229,10 +5229,10 @@
         <v>1.37</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
         <v>19.5</v>
@@ -5241,13 +5241,13 @@
         <v>36</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -5256,10 +5256,10 @@
         <v>30</v>
       </c>
       <c r="AG19" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
         <v>40</v>
@@ -5283,58 +5283,58 @@
         <v>18</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -5468,22 +5468,22 @@
         <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
         <v>22</v>
@@ -5543,10 +5543,10 @@
         <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -5579,7 +5579,7 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BE20" t="n">
         <v>4.2</v>
@@ -5591,22 +5591,22 @@
         <v>4.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5618,41 +5618,41 @@
         <v>12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>20</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H21" t="n">
         <v>2.04</v>
@@ -5695,10 +5695,10 @@
         <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5707,7 +5707,7 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
@@ -5719,10 +5719,10 @@
         <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
         <v>1.79</v>
@@ -5734,7 +5734,7 @@
         <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -5761,7 +5761,7 @@
         <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG21" t="n">
         <v>950</v>
@@ -5788,19 +5788,19 @@
         <v>65</v>
       </c>
       <c r="AO21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT21" t="n">
         <v>3.85</v>
@@ -5824,19 +5824,19 @@
         <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
         <v>4.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD21" t="n">
         <v>4.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
         <v>4.7</v>
@@ -5848,19 +5848,19 @@
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
@@ -5890,23 +5890,23 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
         <v>120</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>24</v>
@@ -6048,7 +6048,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
         <v>32</v>
@@ -6066,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -6078,7 +6078,7 @@
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1144,7 +1144,7 @@
         <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -1159,16 +1159,16 @@
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
@@ -1192,13 +1192,13 @@
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -1225,10 +1225,10 @@
         <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1261,16 +1261,16 @@
         <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1294,13 +1294,13 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
@@ -1312,7 +1312,7 @@
         <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>34</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
         <v>5.5</v>
@@ -1398,19 +1398,19 @@
         <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R4" t="n">
         <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T4" t="n">
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
@@ -1434,7 +1434,7 @@
         <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
@@ -1443,7 +1443,7 @@
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
@@ -1458,13 +1458,13 @@
         <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>9.4</v>
@@ -1476,13 +1476,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>9.4</v>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="n">
         <v>36</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1667,10 +1667,10 @@
         <v>3.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
         <v>160</v>
@@ -1682,7 +1682,7 @@
         <v>85</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
         <v>36</v>
@@ -1709,7 +1709,7 @@
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1721,37 +1721,37 @@
         <v>36</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO5" t="n">
         <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU5" t="n">
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW5" t="n">
         <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
         <v>11</v>
@@ -1760,19 +1760,19 @@
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
@@ -1799,16 +1799,16 @@
         <v>6.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
         <v>18</v>
@@ -1817,16 +1817,16 @@
         <v>5.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
         <v>18.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
         <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I6" t="n">
         <v>3.85</v>
@@ -1909,13 +1909,13 @@
         <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1939,7 +1939,7 @@
         <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
@@ -2026,7 +2026,7 @@
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
@@ -2044,13 +2044,13 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
         <v>5.1</v>
@@ -2089,14 +2089,14 @@
         <v>12</v>
       </c>
       <c r="BZ6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA6" t="n">
         <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.15</v>
       </c>
       <c r="G7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="H7" t="n">
         <v>13.5</v>
@@ -2178,7 +2178,7 @@
         <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>2.44</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.64</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
@@ -2650,7 +2650,7 @@
         <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.17</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.44</v>
       </c>
       <c r="G10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H10" t="n">
         <v>5.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -3397,46 +3397,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G12" t="n">
         <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="I12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="Q12" t="n">
         <v>1.32</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="T12" t="n">
         <v>1.38</v>
@@ -3445,7 +3445,7 @@
         <v>3.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W12" t="n">
         <v>1.35</v>
@@ -3466,13 +3466,13 @@
         <v>80</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
         <v>100</v>
@@ -3484,7 +3484,7 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
         <v>160</v>
@@ -3493,19 +3493,19 @@
         <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>16.5</v>
@@ -3517,7 +3517,7 @@
         <v>19.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU12" t="n">
         <v>10</v>
@@ -3529,7 +3529,7 @@
         <v>13.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
@@ -3541,7 +3541,7 @@
         <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12" t="n">
         <v>24</v>
@@ -3550,77 +3550,77 @@
         <v>22</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU12" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.8</v>
       </c>
       <c r="BV12" t="n">
         <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U13" t="n">
         <v>2.56</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="I14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
@@ -3932,25 +3932,25 @@
         <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
         <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -4013,55 +4013,55 @@
         <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV14" t="n">
         <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF14" t="n">
         <v>6</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.8</v>
       </c>
       <c r="BG14" t="n">
         <v>6.8</v>
@@ -4070,19 +4070,19 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
@@ -4094,41 +4094,41 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>3.3</v>
       </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>1.1</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>2.24</v>
       </c>
       <c r="I15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J15" t="n">
         <v>4.6</v>
@@ -4207,7 +4207,7 @@
         <v>4.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W15" t="n">
         <v>1.56</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
         <v>1.84</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
         <v>3.8</v>
@@ -4443,7 +4443,7 @@
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>2.04</v>
@@ -4455,7 +4455,7 @@
         <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
         <v>1.95</v>
@@ -4491,10 +4491,10 @@
         <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH16" t="n">
         <v>25</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4542,19 +4542,19 @@
         <v>18.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4566,13 +4566,13 @@
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH16" t="n">
         <v>3.25</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I17" t="n">
         <v>3.9</v>
@@ -4700,7 +4700,7 @@
         <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
         <v>1.19</v>
@@ -4712,7 +4712,7 @@
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
@@ -4784,7 +4784,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4805,10 +4805,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB17" t="n">
         <v>27</v>
@@ -4817,7 +4817,7 @@
         <v>25</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
         <v>5.7</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -4927,46 +4927,46 @@
         <v>1.49</v>
       </c>
       <c r="H18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
         <v>4.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
         <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
@@ -4975,7 +4975,7 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
         <v>32</v>
@@ -4987,7 +4987,7 @@
         <v>450</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AC18" t="n">
         <v>12.5</v>
@@ -4996,155 +4996,155 @@
         <v>40</v>
       </c>
       <c r="AE18" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AF18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK18" t="n">
         <v>18.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="n">
         <v>9</v>
       </c>
       <c r="AO18" t="n">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AP18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>26</v>
-      </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
         <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
         <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.84</v>
+        <v>12</v>
       </c>
       <c r="BN18" t="n">
         <v>3.75</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU18" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
         <v>2.16</v>
       </c>
       <c r="I19" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.29</v>
@@ -5199,7 +5199,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
@@ -5214,19 +5214,19 @@
         <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="U19" t="n">
         <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5268,7 +5268,7 @@
         <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
         <v>50</v>
@@ -5283,16 +5283,16 @@
         <v>18</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
         <v>3.55</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT19" t="n">
         <v>3.5</v>
@@ -5307,7 +5307,7 @@
         <v>3.75</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AY19" t="n">
         <v>3.45</v>
@@ -5319,13 +5319,13 @@
         <v>3.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
         <v>3.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE19" t="n">
         <v>4.1</v>
@@ -5334,7 +5334,7 @@
         <v>3.85</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H20" t="n">
         <v>4.6</v>
@@ -5465,10 +5465,10 @@
         <v>1.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
@@ -5600,13 +5600,13 @@
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5621,38 +5621,38 @@
         <v>6</v>
       </c>
       <c r="BR20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
         <v>7.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H21" t="n">
         <v>2.04</v>
@@ -5707,7 +5707,7 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
@@ -5719,22 +5719,22 @@
         <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
         <v>1.79</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -5770,7 +5770,7 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -5791,94 +5791,94 @@
         <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC21" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
         <v>4.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.28</v>
+        <v>5.1</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
@@ -5890,23 +5890,23 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.05</v>
+        <v>2.06</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G22" t="n">
         <v>1.82</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.75</v>
@@ -5988,7 +5988,7 @@
         <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -6003,7 +6003,7 @@
         <v>200</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC22" t="n">
         <v>8.6</v>
@@ -6018,7 +6018,7 @@
         <v>10.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>25</v>
@@ -6030,10 +6030,10 @@
         <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>200</v>
@@ -6048,13 +6048,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
         <v>6.4</v>
@@ -6066,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -6078,7 +6078,7 @@
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6090,13 +6090,13 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
         <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="n">
         <v>3.15</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,76 +857,76 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1.04</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
@@ -935,34 +935,34 @@
         <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
         <v>4.5</v>
@@ -971,116 +971,116 @@
         <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
         <v>4.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS2" t="n">
         <v>5.8</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -1111,43 +1111,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.5</v>
@@ -1162,19 +1162,19 @@
         <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>9.199999999999999</v>
@@ -1192,7 +1192,7 @@
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>18</v>
@@ -1201,19 +1201,19 @@
         <v>320</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>260</v>
@@ -1222,13 +1222,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1252,7 +1252,7 @@
         <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1261,22 +1261,22 @@
         <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.800000000000001</v>
@@ -1294,25 +1294,25 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
         <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>34</v>
@@ -1327,14 +1327,14 @@
         <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA3" t="n">
         <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1395,16 +1395,16 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
         <v>1.74</v>
@@ -1413,22 +1413,22 @@
         <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
         <v>10.5</v>
@@ -1437,10 +1437,10 @@
         <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1449,79 +1449,79 @@
         <v>10</v>
       </c>
       <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>18</v>
       </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>20</v>
-      </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO4" t="n">
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW4" t="n">
         <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
         <v>50</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
         <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
         <v>50</v>
@@ -1530,65 +1530,65 @@
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
         <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>19.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
         <v>2.64</v>
@@ -1652,19 +1652,19 @@
         <v>4.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
         <v>2.42</v>
       </c>
       <c r="S5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="T5" t="n">
         <v>1.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1691,10 +1691,10 @@
         <v>17</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
         <v>36</v>
@@ -1703,22 +1703,22 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AN5" t="n">
         <v>7.4</v>
@@ -1727,52 +1727,52 @@
         <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
@@ -1796,10 +1796,10 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO5" t="n">
         <v>5.4</v>
@@ -1808,7 +1808,7 @@
         <v>16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR5" t="n">
         <v>18</v>
@@ -1826,13 +1826,13 @@
         <v>17.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
         <v>18.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>8.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
         <v>3.85</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
@@ -1900,10 +1900,10 @@
         <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
         <v>2.08</v>
@@ -1924,7 +1924,7 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1951,7 +1951,7 @@
         <v>46</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1978,7 +1978,7 @@
         <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -2014,7 +2014,7 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -2029,28 +2029,28 @@
         <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BH6" t="n">
         <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5.1</v>
@@ -2062,13 +2062,13 @@
         <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
@@ -2080,23 +2080,23 @@
         <v>29</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G7" t="n">
         <v>1.2</v>
       </c>
       <c r="H7" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
@@ -2169,7 +2169,7 @@
         <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
         <v>2.26</v>
@@ -2202,7 +2202,7 @@
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF7" t="n">
         <v>20</v>
@@ -2223,7 +2223,7 @@
         <v>17.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -2232,16 +2232,16 @@
         <v>2.18</v>
       </c>
       <c r="AO7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
         <v>6.6</v>
@@ -2253,31 +2253,31 @@
         <v>21</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW7" t="n">
         <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
         <v>6.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.26</v>
@@ -2423,16 +2423,16 @@
         <v>1.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
         <v>3.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2489,64 +2489,64 @@
         <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="AV8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BC8" t="n">
         <v>2.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BD8" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2558,25 +2558,25 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
         <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.17</v>
@@ -2680,7 +2680,7 @@
         <v>1.44</v>
       </c>
       <c r="U9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2692,7 +2692,7 @@
         <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2716,7 +2716,7 @@
         <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
         <v>19.5</v>
@@ -2740,31 +2740,31 @@
         <v>5.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>290</v>
+        <v>30</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="AX9" t="n">
         <v>8.4</v>
@@ -2776,7 +2776,7 @@
         <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BB9" t="n">
         <v>10.5</v>
@@ -2785,25 +2785,25 @@
         <v>8.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF9" t="n">
         <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK9" t="n">
         <v>4.8</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>5.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.59</v>
+        <v>6.4</v>
       </c>
       <c r="BT9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>9.6</v>
       </c>
-      <c r="BU9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G10" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.13</v>
@@ -2913,70 +2913,70 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R10" t="n">
         <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="T10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="U10" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="X10" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Y10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
         <v>22</v>
@@ -2991,46 +2991,46 @@
         <v>50</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -3042,34 +3042,34 @@
         <v>14</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BG10" t="n">
         <v>20</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BL10" t="n">
         <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
         <v>4.2</v>
@@ -3078,41 +3078,41 @@
         <v>10</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR10" t="n">
         <v>16</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT10" t="n">
         <v>12</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY10" t="n">
         <v>5.6</v>
       </c>
-      <c r="BX10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY10" t="n">
+      <c r="BZ10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="CA10" t="n">
         <v>5.4</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
         <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>55</v>
@@ -3251,7 +3251,7 @@
         <v>6.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>16</v>
@@ -3260,46 +3260,46 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
         <v>14.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG11" t="n">
         <v>5.5</v>
@@ -3308,7 +3308,7 @@
         <v>7.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.199999999999999</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
         <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I12" t="n">
         <v>2.04</v>
@@ -3421,28 +3421,28 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="R12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S12" t="n">
         <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.96</v>
@@ -3454,7 +3454,7 @@
         <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
@@ -3487,7 +3487,7 @@
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>85</v>
@@ -3496,103 +3496,103 @@
         <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="BH12" t="n">
         <v>6.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>8.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
         <v>6.2</v>
@@ -3604,23 +3604,23 @@
         <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BX12" t="n">
         <v>17</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G13" t="n">
         <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
@@ -3693,10 +3693,10 @@
         <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
@@ -3759,31 +3759,31 @@
         <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AW13" t="n">
         <v>4.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY13" t="n">
         <v>7</v>
@@ -3792,7 +3792,7 @@
         <v>5.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB13" t="n">
         <v>5.8</v>
@@ -3801,10 +3801,10 @@
         <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="BF13" t="n">
         <v>3.9</v>
@@ -3840,7 +3840,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.23</v>
+        <v>3.65</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.24</v>
@@ -3929,7 +3929,7 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.17</v>
@@ -4013,61 +4013,61 @@
         <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV14" t="n">
         <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6</v>
-      </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF14" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6</v>
       </c>
       <c r="BG14" t="n">
         <v>6.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI14" t="n">
         <v>3.6</v>
@@ -4076,31 +4076,31 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="BT14" t="n">
         <v>5.5</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J15" t="n">
         <v>4.6</v>
@@ -4183,31 +4183,31 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.05</v>
       </c>
       <c r="P15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="U15" t="n">
         <v>4.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W15" t="n">
         <v>1.56</v>
@@ -4225,7 +4225,7 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC15" t="n">
         <v>950</v>
@@ -4234,7 +4234,7 @@
         <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
         <v>500</v>
@@ -4267,55 +4267,55 @@
         <v>5.9</v>
       </c>
       <c r="AP15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AU15" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BG15" t="n">
         <v>4.6</v>
@@ -4324,7 +4324,7 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
         <v>1.84</v>
@@ -4428,7 +4428,7 @@
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>1.36</v>
@@ -4437,31 +4437,31 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
         <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
         <v>2.18</v>
@@ -4470,16 +4470,16 @@
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
         <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -4491,31 +4491,31 @@
         <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO16" t="n">
         <v>130</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4542,7 +4542,7 @@
         <v>18.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4563,22 +4563,22 @@
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
         <v>3.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4590,53 +4590,53 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BR16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -4676,13 +4676,13 @@
         <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L17" t="n">
         <v>1.6</v>
@@ -4691,7 +4691,7 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
@@ -4700,16 +4700,16 @@
         <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
         <v>1.8</v>
@@ -4784,7 +4784,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4805,10 +4805,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
         <v>27</v>
@@ -4817,7 +4817,7 @@
         <v>25</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
         <v>5.7</v>
@@ -4883,14 +4883,14 @@
         <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
         <v>13.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -4921,73 +4921,73 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="H18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="X18" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA18" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AB18" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC18" t="n">
         <v>12.5</v>
@@ -4996,109 +4996,109 @@
         <v>40</v>
       </c>
       <c r="AE18" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AF18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AJ18" t="n">
         <v>13.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AN18" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AO18" t="n">
         <v>420</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
         <v>6.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
         <v>10.5</v>
       </c>
       <c r="BC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>12</v>
       </c>
       <c r="BN18" t="n">
         <v>3.75</v>
@@ -5107,19 +5107,19 @@
         <v>3</v>
       </c>
       <c r="BP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
         <v>9.4</v>
       </c>
-      <c r="BQ18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>9</v>
-      </c>
       <c r="BT18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU18" t="n">
         <v>6.4</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
         <v>3.55</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT19" t="n">
         <v>3.5</v>
@@ -5307,7 +5307,7 @@
         <v>3.75</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY19" t="n">
         <v>3.45</v>
@@ -5316,16 +5316,16 @@
         <v>3.55</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC19" t="n">
         <v>3.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
         <v>4.1</v>
@@ -5337,7 +5337,7 @@
         <v>11</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI19" t="n">
         <v>3</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G20" t="n">
         <v>1.83</v>
@@ -5456,19 +5456,19 @@
         <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
         <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
@@ -5480,7 +5480,7 @@
         <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -5498,7 +5498,7 @@
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
         <v>23</v>
@@ -5543,7 +5543,7 @@
         <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS20" t="n">
         <v>4.3</v>
@@ -5558,7 +5558,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
         <v>8.6</v>
@@ -5570,7 +5570,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
@@ -5579,34 +5579,34 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE20" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.2</v>
       </c>
       <c r="BF20" t="n">
         <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="n">
         <v>3.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5624,35 +5624,35 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA20" t="n">
         <v>7.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -5683,31 +5683,31 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G21" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H21" t="n">
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
@@ -5731,16 +5731,16 @@
         <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
         <v>15.5</v>
@@ -5758,7 +5758,7 @@
         <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
         <v>34</v>
@@ -5788,64 +5788,64 @@
         <v>65</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS21" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AT21" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.7</v>
+        <v>2.82</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>2.88</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>2.94</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BH21" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BI21" t="n">
         <v>2.78</v>
@@ -5854,37 +5854,37 @@
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5896,17 +5896,17 @@
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.29</v>
+        <v>2.06</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>
@@ -5937,43 +5937,43 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G22" t="n">
         <v>1.82</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
         <v>4.3</v>
@@ -5982,13 +5982,13 @@
         <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V22" t="n">
         <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -6003,7 +6003,7 @@
         <v>200</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC22" t="n">
         <v>8.6</v>
@@ -6018,10 +6018,10 @@
         <v>10.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
         <v>120</v>
@@ -6033,13 +6033,13 @@
         <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO22" t="n">
         <v>170</v>
@@ -6048,16 +6048,16 @@
         <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
@@ -6066,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -6075,10 +6075,10 @@
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6090,13 +6090,13 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
         <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="n">
         <v>3.15</v>
@@ -6147,7 +6147,7 @@
         <v>9.4</v>
       </c>
       <c r="BX22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
         <v>9.800000000000001</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
@@ -914,10 +914,10 @@
         <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -926,10 +926,10 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>95</v>
@@ -938,7 +938,7 @@
         <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
@@ -959,52 +959,52 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
         <v>5.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
         <v>5.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
         <v>5.6</v>
@@ -1016,71 +1016,71 @@
         <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
         <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BV2" t="n">
         <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>36</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
@@ -1129,40 +1129,40 @@
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1171,19 +1171,19 @@
         <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
@@ -1198,7 +1198,7 @@
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -1207,7 +1207,7 @@
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1216,79 +1216,79 @@
         <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
@@ -1297,13 +1297,13 @@
         <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
         <v>10.5</v>
@@ -1312,19 +1312,19 @@
         <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
         <v>11</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
         <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1392,55 +1392,55 @@
         <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1452,10 +1452,10 @@
         <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1464,34 +1464,34 @@
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>50</v>
@@ -1500,10 +1500,10 @@
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
         <v>50</v>
@@ -1512,16 +1512,16 @@
         <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>27</v>
       </c>
       <c r="BE4" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
         <v>50</v>
@@ -1530,19 +1530,19 @@
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
@@ -1551,16 +1551,16 @@
         <v>3.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
         <v>25</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
@@ -1569,26 +1569,26 @@
         <v>6.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1637,25 +1637,25 @@
         <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.07</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1.23</v>
       </c>
       <c r="R5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S5" t="n">
         <v>1.56</v>
@@ -1664,28 +1664,28 @@
         <v>1.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
         <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="n">
         <v>17</v>
@@ -1697,7 +1697,7 @@
         <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1721,22 +1721,22 @@
         <v>32</v>
       </c>
       <c r="AN5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP5" t="n">
         <v>7.4</v>
       </c>
-      <c r="AO5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AQ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR5" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR5" t="n">
-        <v>22</v>
-      </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>21</v>
@@ -1745,76 +1745,76 @@
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="AW5" t="n">
         <v>16.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
         <v>7.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BN5" t="n">
         <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR5" t="n">
         <v>18</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT5" t="n">
         <v>8</v>
@@ -1823,26 +1823,26 @@
         <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
         <v>3.85</v>
@@ -1891,13 +1891,13 @@
         <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
@@ -1912,10 +1912,10 @@
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1924,7 +1924,7 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1963,7 +1963,7 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
@@ -1975,19 +1975,19 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
         <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
         <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS6" t="n">
         <v>60</v>
@@ -2011,10 +2011,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -2023,13 +2023,13 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
         <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG6" t="n">
         <v>36</v>
@@ -2038,37 +2038,37 @@
         <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP6" t="n">
         <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
@@ -2077,26 +2077,26 @@
         <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2127,43 +2127,43 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.05</v>
       </c>
       <c r="P7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R7" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="S7" t="n">
         <v>1.45</v>
@@ -2172,7 +2172,7 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
         <v>1.05</v>
@@ -2202,7 +2202,7 @@
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF7" t="n">
         <v>20</v>
@@ -2229,22 +2229,22 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AO7" t="n">
         <v>140</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>19.5</v>
@@ -2253,34 +2253,34 @@
         <v>21</v>
       </c>
       <c r="AV7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5</v>
       </c>
-      <c r="AY7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
         <v>1.96</v>
@@ -2289,7 +2289,7 @@
         <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI7" t="n">
         <v>4.7</v>
@@ -2298,59 +2298,59 @@
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
         <v>6.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT7" t="n">
         <v>20</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>4.7</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -2411,28 +2411,28 @@
         <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R8" t="n">
         <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
         <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2483,82 +2483,82 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
         <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.28</v>
+        <v>5.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.56</v>
+        <v>1.97</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.48</v>
+        <v>1.99</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.14</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2635,52 +2635,52 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2701,10 +2701,10 @@
         <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2713,13 +2713,13 @@
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AG9" t="n">
         <v>17.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2728,7 +2728,7 @@
         <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
         <v>46</v>
@@ -2737,37 +2737,37 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2776,31 +2776,31 @@
         <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
         <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="BE9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH9" t="n">
         <v>5.8</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>6</v>
-      </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>9</v>
@@ -2812,13 +2812,13 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
         <v>10.5</v>
@@ -2827,7 +2827,7 @@
         <v>5.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BS9" t="n">
         <v>6.4</v>
@@ -2839,26 +2839,26 @@
         <v>5</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY9" t="n">
         <v>7.8</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
         <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
         <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K10" t="n">
         <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
@@ -2916,37 +2916,37 @@
         <v>10.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
         <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="U10" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="X10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z10" t="n">
         <v>160</v>
@@ -2955,22 +2955,22 @@
         <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC10" t="n">
         <v>21</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
         <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2979,140 +2979,140 @@
         <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
         <v>50</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AO10" t="n">
         <v>30</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
         <v>12.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BK10" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BL10" t="n">
         <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BR10" t="n">
         <v>16</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
         <v>36</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BX10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>7.8</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
         <v>4.5</v>
@@ -3161,25 +3161,25 @@
         <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>1.07</v>
       </c>
       <c r="P11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
         <v>1.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
         <v>1.6</v>
@@ -3191,10 +3191,10 @@
         <v>3.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
         <v>500</v>
@@ -3203,7 +3203,7 @@
         <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA11" t="n">
         <v>120</v>
@@ -3224,34 +3224,34 @@
         <v>190</v>
       </c>
       <c r="AG11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI11" t="n">
         <v>22</v>
       </c>
       <c r="AJ11" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AM11" t="n">
         <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO11" t="n">
         <v>6.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>16</v>
@@ -3260,52 +3260,52 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
         <v>14.5</v>
       </c>
       <c r="BF11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH11" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>7.2</v>
       </c>
       <c r="BI11" t="n">
         <v>5.5</v>
@@ -3314,40 +3314,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN11" t="n">
         <v>8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP11" t="n">
         <v>18</v>
       </c>
       <c r="BQ11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS11" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
         <v>7.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW11" t="n">
         <v>6</v>
@@ -3356,17 +3356,17 @@
         <v>17</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
@@ -3415,37 +3415,37 @@
         <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="T12" t="n">
         <v>1.36</v>
       </c>
       <c r="U12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W12" t="n">
         <v>1.35</v>
@@ -3463,10 +3463,10 @@
         <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
@@ -3475,16 +3475,16 @@
         <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH12" t="n">
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
@@ -3499,128 +3499,128 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AP12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX12" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
         <v>17.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
         <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN12" t="n">
         <v>8.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
         <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV12" t="n">
         <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX12" t="n">
         <v>17</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -3669,13 +3669,13 @@
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
@@ -3684,25 +3684,25 @@
         <v>2.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3720,7 +3720,7 @@
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
@@ -3759,55 +3759,55 @@
         <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY13" t="n">
         <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
         <v>4.5</v>
@@ -3816,65 +3816,65 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.65</v>
+        <v>1.75</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G14" t="n">
         <v>4.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
@@ -3923,28 +3923,28 @@
         <v>4.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
         <v>1.54</v>
@@ -3962,10 +3962,10 @@
         <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3974,10 +3974,10 @@
         <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
         <v>970</v>
@@ -3986,16 +3986,16 @@
         <v>500</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>500</v>
@@ -4010,125 +4010,125 @@
         <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG14" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI14" t="n">
         <v>3.6</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.64</v>
+        <v>4.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2.86</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU14" t="n">
         <v>4.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -4186,31 +4186,31 @@
         <v>13.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P15" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="U15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4225,7 +4225,7 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
         <v>950</v>
@@ -4234,7 +4234,7 @@
         <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
         <v>500</v>
@@ -4258,73 +4258,73 @@
         <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.9</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,19 +4336,19 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.47</v>
+        <v>2.94</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4360,29 +4360,29 @@
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4422,22 +4422,22 @@
         <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>1.36</v>
@@ -4446,19 +4446,19 @@
         <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
         <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.22</v>
@@ -4473,13 +4473,13 @@
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
         <v>170</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
         <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
         <v>10.5</v>
@@ -4518,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP16" t="n">
         <v>11.5</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4542,7 +4542,7 @@
         <v>18.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4563,22 +4563,22 @@
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
         <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="n">
         <v>3.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4590,13 +4590,13 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN16" t="n">
         <v>4.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP16" t="n">
         <v>12.5</v>
@@ -4608,7 +4608,7 @@
         <v>29</v>
       </c>
       <c r="BS16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
@@ -4623,7 +4623,7 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>15</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -4691,142 +4691,142 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
         <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI17" t="n">
         <v>95</v>
       </c>
-      <c r="AB17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
       <c r="AJ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK17" t="n">
         <v>38</v>
       </c>
-      <c r="AK17" t="n">
-        <v>44</v>
-      </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP17" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="n">
         <v>2.66</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4921,230 +4921,230 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="G18" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I18" t="n">
         <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.44</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="n">
         <v>480</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AJ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN18" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AO18" t="n">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>7</v>
       </c>
-      <c r="AS18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="BA18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BB18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
         <v>3.6</v>
@@ -5187,52 +5187,52 @@
         <v>2.46</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R19" t="n">
         <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
         <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
         <v>19.5</v>
@@ -5244,10 +5244,10 @@
         <v>950</v>
       </c>
       <c r="AC19" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -5268,55 +5268,55 @@
         <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
         <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
         <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY19" t="n">
         <v>3.5</v>
       </c>
-      <c r="AU19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB19" t="n">
         <v>4.1</v>
@@ -5328,13 +5328,13 @@
         <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BH19" t="n">
         <v>3.95</v>
@@ -5355,7 +5355,7 @@
         <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO19" t="n">
         <v>1.04</v>
@@ -5373,7 +5373,7 @@
         <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU19" t="n">
         <v>1.04</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5429,52 +5429,52 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
@@ -5492,10 +5492,10 @@
         <v>46</v>
       </c>
       <c r="AA20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -5504,7 +5504,7 @@
         <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
@@ -5516,7 +5516,7 @@
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
         <v>23</v>
@@ -5528,73 +5528,73 @@
         <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO20" t="n">
         <v>75</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF20" t="n">
         <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
@@ -5615,10 +5615,10 @@
         <v>3.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
@@ -5627,10 +5627,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5645,14 +5645,14 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA20" t="n">
         <v>7.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5683,55 +5683,55 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="G21" t="n">
         <v>4.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
         <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="W21" t="n">
         <v>1.27</v>
@@ -5740,13 +5740,13 @@
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AB21" t="n">
         <v>950</v>
@@ -5761,7 +5761,7 @@
         <v>27</v>
       </c>
       <c r="AF21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG21" t="n">
         <v>950</v>
@@ -5770,85 +5770,85 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO21" t="n">
         <v>19.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AR21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.85</v>
+        <v>2.82</v>
       </c>
       <c r="AX21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AY21" t="n">
         <v>2.76</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH21" t="n">
         <v>3.65</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BC21" t="n">
+      <c r="BI21" t="n">
         <v>2.88</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.78</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
@@ -5860,53 +5860,53 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.89</v>
+        <v>1.21</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>2.06</v>
+        <v>5.7</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5937,55 +5937,55 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G22" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
         <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
         <v>1.96</v>
@@ -6006,7 +6006,7 @@
         <v>7.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD22" t="n">
         <v>24</v>
@@ -6051,10 +6051,10 @@
         <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
         <v>6.2</v>
@@ -6066,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -6075,10 +6075,10 @@
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6090,16 +6090,16 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
         <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI22" t="n">
         <v>2.48</v>
@@ -6108,13 +6108,13 @@
         <v>11.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN22" t="n">
         <v>4.4</v>
@@ -6126,41 +6126,41 @@
         <v>14</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR22" t="n">
         <v>34</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT22" t="n">
         <v>9</v>
       </c>
       <c r="BU22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ22" t="n">
         <v>32</v>
       </c>
       <c r="CA22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,79 +857,79 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.95</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>95</v>
@@ -941,16 +941,16 @@
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
         <v>85</v>
@@ -959,128 +959,128 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN2" t="n">
         <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
         <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>6</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -1141,13 +1141,13 @@
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3.7</v>
@@ -1159,37 +1159,37 @@
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y3" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>15</v>
-      </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1198,133 +1198,133 @@
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>40</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
         <v>48</v>
       </c>
       <c r="BB3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC3" t="n">
         <v>21</v>
       </c>
-      <c r="BC3" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
         <v>10.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
         <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
@@ -1431,31 +1431,31 @@
         <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1464,10 +1464,10 @@
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1482,31 +1482,31 @@
         <v>38</v>
       </c>
       <c r="AS4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV4" t="n">
         <v>18.5</v>
       </c>
-      <c r="AT4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>19</v>
-      </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1521,10 +1521,10 @@
         <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.72</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.74</v>
-      </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="O5" t="n">
         <v>1.07</v>
       </c>
       <c r="P5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q5" t="n">
         <v>1.23</v>
@@ -1658,19 +1658,19 @@
         <v>2.44</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="T5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="U5" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1679,7 +1679,7 @@
         <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>120</v>
@@ -1688,10 +1688,10 @@
         <v>80</v>
       </c>
       <c r="AC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
@@ -1700,10 +1700,10 @@
         <v>85</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>24</v>
@@ -1715,134 +1715,134 @@
         <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP5" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
         <v>6</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN5" t="n">
         <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU5" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>16.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CA5" t="n">
         <v>5.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
         <v>3.85</v>
@@ -1891,46 +1891,46 @@
         <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>26</v>
@@ -1939,7 +1939,7 @@
         <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
@@ -1948,7 +1948,7 @@
         <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
         <v>13.5</v>
@@ -1957,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
@@ -1966,34 +1966,34 @@
         <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
@@ -2014,43 +2014,43 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
         <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG6" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5</v>
@@ -2059,16 +2059,16 @@
         <v>3.85</v>
       </c>
       <c r="BP6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>8.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
@@ -2077,26 +2077,26 @@
         <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
         <v>10.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA6" t="n">
         <v>10.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="I7" t="n">
-        <v>18.5</v>
+        <v>9.6</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>1.13</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2187,170 +2187,170 @@
         <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AE7" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AF7" t="n">
         <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>16</v>
       </c>
-      <c r="AK7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>2.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.7</v>
+        <v>2.28</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>5.6</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BR7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="BT7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9</v>
+        <v>2.98</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>3.15</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="I8" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P8" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="S8" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="T8" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>160</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL8" t="n">
         <v>42</v>
       </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BM8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CA8" t="n">
         <v>5.3</v>
       </c>
-      <c r="BA8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>4.5</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2659,28 +2659,28 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2692,7 +2692,7 @@
         <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2701,145 +2701,145 @@
         <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>42</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>290</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT9" t="n">
         <v>15.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
       </c>
       <c r="AX9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>21</v>
-      </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW9" t="n">
         <v>8</v>
@@ -2851,14 +2851,14 @@
         <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UMF Tindstoll</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X10" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5.4</v>
       </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>4.4</v>
       </c>
-      <c r="BL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I11" t="n">
         <v>2.44</v>
@@ -3173,19 +3173,19 @@
         <v>1.07</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U11" t="n">
         <v>3.7</v>
@@ -3194,16 +3194,16 @@
         <v>1.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
         <v>500</v>
       </c>
       <c r="Y11" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="Z11" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA11" t="n">
         <v>120</v>
@@ -3230,7 +3230,7 @@
         <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AJ11" t="n">
         <v>230</v>
@@ -3239,19 +3239,19 @@
         <v>70</v>
       </c>
       <c r="AL11" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO11" t="n">
         <v>6.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>16</v>
@@ -3260,10 +3260,10 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>13.5</v>
@@ -3275,7 +3275,7 @@
         <v>17.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
@@ -3287,7 +3287,7 @@
         <v>17.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
@@ -3302,13 +3302,13 @@
         <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH11" t="n">
         <v>7.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.199999999999999</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN11" t="n">
         <v>8</v>
@@ -3329,28 +3329,28 @@
         <v>4.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
         <v>6.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS11" t="n">
         <v>6.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV11" t="n">
         <v>15</v>
       </c>
       <c r="BW11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX11" t="n">
         <v>17</v>
@@ -3359,14 +3359,14 @@
         <v>6.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="I12" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
@@ -3427,7 +3427,7 @@
         <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q12" t="n">
         <v>1.3</v>
@@ -3436,19 +3436,19 @@
         <v>2.14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="T12" t="n">
         <v>1.36</v>
       </c>
       <c r="U12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>55</v>
@@ -3469,13 +3469,13 @@
         <v>15</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AG12" t="n">
         <v>18.5</v>
@@ -3499,25 +3499,25 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS12" t="n">
         <v>19.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
@@ -3526,31 +3526,31 @@
         <v>5.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
         <v>17.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD12" t="n">
         <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>11.5</v>
@@ -3559,68 +3559,68 @@
         <v>5</v>
       </c>
       <c r="BH12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BN12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
         <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV12" t="n">
         <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BX12" t="n">
         <v>17</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
         <v>5.2</v>
@@ -3675,34 +3675,34 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="U13" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3717,7 +3717,7 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
         <v>20</v>
@@ -3729,7 +3729,7 @@
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
         <v>36</v>
@@ -3744,7 +3744,7 @@
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -3756,67 +3756,67 @@
         <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
         <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.75</v>
+        <v>5.1</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.55</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -3905,52 +3905,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="I14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="n">
         <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,43 +3959,43 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA14" t="n">
         <v>500</v>
       </c>
-      <c r="AA14" t="n">
-        <v>900</v>
-      </c>
       <c r="AB14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC14" t="n">
         <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
         <v>500</v>
       </c>
       <c r="AG14" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AH14" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
         <v>500</v>
@@ -4007,109 +4007,109 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AW14" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AX14" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BA14" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BT14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW14" t="n">
         <v>5.2</v>
@@ -4118,17 +4118,17 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H15" t="n">
         <v>2.18</v>
@@ -4177,7 +4177,7 @@
         <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -4186,25 +4186,25 @@
         <v>13.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P15" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="R15" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="S15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.71</v>
@@ -4228,7 +4228,7 @@
         <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
         <v>970</v>
@@ -4267,64 +4267,64 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.66</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.67</v>
+        <v>2.52</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.65</v>
+        <v>2.58</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.79</v>
+        <v>5.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.69</v>
+        <v>4.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.73</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.71</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.71</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,13 +4336,13 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.94</v>
+        <v>2.46</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4360,7 +4360,7 @@
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
         <v>5.4</v>
@@ -4464,13 +4464,13 @@
         <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
         <v>50</v>
@@ -4482,16 +4482,16 @@
         <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>9.800000000000001</v>
@@ -4503,10 +4503,10 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>40</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -4539,10 +4539,10 @@
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4551,10 +4551,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4563,22 +4563,22 @@
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
         <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
         <v>3.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4590,13 +4590,13 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
         <v>12.5</v>
@@ -4608,7 +4608,7 @@
         <v>29</v>
       </c>
       <c r="BS16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
@@ -4617,7 +4617,7 @@
         <v>6</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW16" t="n">
         <v>14</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
         <v>3.75</v>
@@ -4697,64 +4697,64 @@
         <v>1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q17" t="n">
         <v>2.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
         <v>5.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
         <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB17" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8</v>
-      </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>65</v>
       </c>
       <c r="AF17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG17" t="n">
         <v>15</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
         <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
         <v>36</v>
@@ -4772,25 +4772,25 @@
         <v>42</v>
       </c>
       <c r="AO17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
         <v>15</v>
@@ -4808,25 +4808,25 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>70</v>
       </c>
       <c r="BB17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
         <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="n">
         <v>2.66</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BN17" t="n">
         <v>5.1</v>
@@ -4856,7 +4856,7 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4880,17 +4880,17 @@
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA17" t="n">
         <v>13.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -4921,230 +4921,230 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="G18" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>10.5</v>
       </c>
       <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.85</v>
       </c>
-      <c r="K18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.92</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
         <v>85</v>
       </c>
       <c r="AA18" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AF18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
         <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>510</v>
+        <v>270</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="AR18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
+      <c r="BF18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>12</v>
       </c>
-      <c r="BC18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF18" t="n">
+      <c r="BK18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP18" t="n">
         <v>10</v>
       </c>
-      <c r="BG18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G19" t="n">
         <v>3.05</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="H19" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="I19" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.34</v>
@@ -5202,139 +5202,139 @@
         <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
         <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AB19" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AR19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC19" t="n">
         <v>21</v>
       </c>
-      <c r="AT19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
         <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>3.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BH19" t="n">
         <v>3.95</v>
@@ -5343,52 +5343,52 @@
         <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G20" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.36</v>
@@ -5477,10 +5477,10 @@
         <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -5495,7 +5495,7 @@
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -5507,10 +5507,10 @@
         <v>70</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -5519,7 +5519,7 @@
         <v>70</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK20" t="n">
         <v>22</v>
@@ -5543,10 +5543,10 @@
         <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -5558,10 +5558,10 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
@@ -5570,43 +5570,43 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
         <v>15.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
         <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH20" t="n">
         <v>3.75</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5615,7 +5615,7 @@
         <v>3.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ20" t="n">
         <v>6.2</v>
@@ -5624,35 +5624,35 @@
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT20" t="n">
         <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G21" t="n">
         <v>4.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I21" t="n">
         <v>2.06</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.4</v>
@@ -5710,31 +5710,31 @@
         <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
         <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
         <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.94</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -5743,7 +5743,7 @@
         <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA21" t="n">
         <v>24</v>
@@ -5758,10 +5758,10 @@
         <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG21" t="n">
         <v>950</v>
@@ -5776,7 +5776,7 @@
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL21" t="n">
         <v>65</v>
@@ -5785,67 +5785,67 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO21" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.8</v>
+        <v>2.72</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AT21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BC21" t="n">
         <v>3.1</v>
       </c>
-      <c r="AU21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AZ21" t="n">
+      <c r="BD21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE21" t="n">
         <v>3.2</v>
       </c>
-      <c r="BA21" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BF21" t="n">
         <v>3.1</v>
       </c>
-      <c r="BC21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BI21" t="n">
         <v>2.88</v>
@@ -5854,34 +5854,34 @@
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU21" t="n">
         <v>3.7</v>
@@ -5890,277 +5890,785 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
         <v>1.31</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Union Omaha</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-10 05:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G23" t="n">
         <v>1.86</v>
       </c>
-      <c r="H22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L23" t="n">
         <v>1.5</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>1.1</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>3.15</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>1.43</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.32</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1.26</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN23" t="n">
         <v>4.4</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="BO23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR23" t="n">
         <v>34</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="BS23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT23" t="n">
         <v>9</v>
       </c>
-      <c r="AT22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD22" t="n">
+      <c r="BU23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ23" t="n">
         <v>32</v>
       </c>
-      <c r="BE22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG22" t="n">
+      <c r="CA23" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BH22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-06-10 03:05:10</t>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-10 05:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Boise Cutthroats FC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Richmond Kickers</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I24" t="n">
+        <v>990</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K24" t="n">
+        <v>950</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
         <v>3.95</v>
@@ -878,10 +878,10 @@
         <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
@@ -890,7 +890,7 @@
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
@@ -899,16 +899,16 @@
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
         <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
@@ -950,7 +950,7 @@
         <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
         <v>85</v>
@@ -971,10 +971,10 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -998,10 +998,10 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -1010,77 +1010,77 @@
         <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
         <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
         <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>32</v>
       </c>
       <c r="BW2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>6</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>6.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>34</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
         <v>3.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.34</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
         <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
         <v>13.5</v>
@@ -1177,46 +1177,46 @@
         <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
@@ -1225,7 +1225,7 @@
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1234,7 +1234,7 @@
         <v>8.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -1243,7 +1243,7 @@
         <v>40</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,10 +1252,10 @@
         <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
         <v>21</v>
@@ -1264,16 +1264,16 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
         <v>2.78</v>
@@ -1282,59 +1282,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BL3" t="n">
         <v>130</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BR3" t="n">
         <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -1374,52 +1374,52 @@
         <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
         <v>21</v>
@@ -1428,34 +1428,34 @@
         <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1467,13 +1467,13 @@
         <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
@@ -1488,10 +1488,10 @@
         <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>55</v>
@@ -1506,10 +1506,10 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC4" t="n">
         <v>15</v>
@@ -1521,74 +1521,74 @@
         <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
         <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -1619,91 +1619,91 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
         <v>2.72</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="V5" t="n">
         <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>24</v>
@@ -1715,79 +1715,79 @@
         <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR5" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
         <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX5" t="n">
         <v>13</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AY5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB5" t="n">
         <v>19</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF5" t="n">
         <v>7</v>
       </c>
-      <c r="BF5" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK5" t="n">
         <v>5.8</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN5" t="n">
         <v>7.2</v>
       </c>
-      <c r="BN5" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BO5" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP5" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BS5" t="n">
         <v>5.8</v>
       </c>
-      <c r="BR5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6</v>
-      </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>16.5</v>
       </c>
       <c r="BW5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BY5" t="n">
         <v>5.8</v>
       </c>
-      <c r="BX5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>6</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
@@ -1906,7 +1906,7 @@
         <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
@@ -1927,10 +1927,10 @@
         <v>1.8</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
         <v>26</v>
@@ -1945,19 +1945,19 @@
         <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
         <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
@@ -1966,7 +1966,7 @@
         <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
         <v>42</v>
@@ -1975,13 +1975,13 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>12</v>
@@ -2002,7 +2002,7 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -2011,10 +2011,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -2029,40 +2029,40 @@
         <v>60</v>
       </c>
       <c r="BF6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR6" t="n">
         <v>34</v>
@@ -2074,29 +2074,29 @@
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
         <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>44</v>
       </c>
       <c r="BY6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.07</v>
       </c>
-      <c r="P7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W7" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2187,170 +2187,170 @@
         <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AA7" t="n">
-        <v>280</v>
+        <v>470</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AC7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AD7" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AE7" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AF7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK7" t="n">
         <v>20</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AL7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>13</v>
       </c>
-      <c r="AH7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.28</v>
+        <v>3.85</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="BN7" t="n">
         <v>5.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>5.6</v>
       </c>
-      <c r="BR7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA7" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="S8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="Y8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AB8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
         <v>14.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>22</v>
       </c>
-      <c r="AM8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS8" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AU8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA8" t="n">
         <v>18</v>
       </c>
-      <c r="AW8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BL8" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BM8" t="n">
         <v>6.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BS8" t="n">
         <v>4.9</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BX8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -2635,52 +2635,52 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U9" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2692,7 +2692,7 @@
         <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2701,164 +2701,164 @@
         <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>19.5</v>
       </c>
       <c r="AK9" t="n">
         <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV9" t="n">
         <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB9" t="n">
         <v>14</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>15.5</v>
       </c>
       <c r="BC9" t="n">
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR9" t="n">
         <v>17.5</v>
       </c>
-      <c r="BE9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BS9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
         <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -2892,55 +2892,55 @@
         <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
         <v>6.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="U10" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2997,64 +2997,64 @@
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.93</v>
+        <v>5.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.99</v>
+        <v>5.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.14</v>
+        <v>5.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.02</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
@@ -3066,25 +3066,25 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.62</v>
+        <v>3.35</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.62</v>
+        <v>3.35</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -3146,58 +3146,58 @@
         <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H11" t="n">
         <v>2.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="R11" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="Y11" t="n">
         <v>95</v>
@@ -3212,25 +3212,25 @@
         <v>85</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
         <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AG11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
         <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AJ11" t="n">
         <v>230</v>
@@ -3239,112 +3239,112 @@
         <v>70</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AM11" t="n">
         <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AU11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
         <v>17.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE11" t="n">
         <v>21</v>
       </c>
-      <c r="BD11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
         <v>15</v>
@@ -3353,20 +3353,20 @@
         <v>6.2</v>
       </c>
       <c r="BX11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CA11" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>3.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
@@ -3424,37 +3424,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
         <v>1.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U12" t="n">
         <v>3.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
@@ -3469,10 +3469,10 @@
         <v>15</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
         <v>100</v>
@@ -3484,10 +3484,10 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK12" t="n">
         <v>85</v>
@@ -3499,112 +3499,112 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>17.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
         <v>5</v>
       </c>
       <c r="BH12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>8.4</v>
       </c>
       <c r="BO12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU12" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.7</v>
       </c>
       <c r="BV12" t="n">
         <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX12" t="n">
         <v>17</v>
@@ -3613,14 +3613,14 @@
         <v>6.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CA12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V13" t="n">
         <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3717,19 +3717,19 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
         <v>36</v>
@@ -3753,34 +3753,34 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
         <v>7.6</v>
@@ -3789,64 +3789,64 @@
         <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.52</v>
+        <v>7.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.79</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
@@ -3858,23 +3858,23 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.19</v>
+        <v>1.74</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
@@ -3914,43 +3914,43 @@
         <v>1.92</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3959,10 +3959,10 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
         <v>55</v>
@@ -3974,13 +3974,13 @@
         <v>500</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
         <v>500</v>
@@ -4010,10 +4010,10 @@
         <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
         <v>11.5</v>
@@ -4022,22 +4022,22 @@
         <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
         <v>13.5</v>
@@ -4052,31 +4052,31 @@
         <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,10 +4085,10 @@
         <v>7.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4103,32 +4103,32 @@
         <v>6.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW14" t="n">
         <v>5.2</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY14" t="n">
         <v>6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H15" t="n">
         <v>2.18</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
         <v>5.4</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="O15" t="n">
         <v>1.05</v>
@@ -4192,16 +4192,16 @@
         <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="U15" t="n">
         <v>4.2</v>
@@ -4210,7 +4210,7 @@
         <v>1.71</v>
       </c>
       <c r="W15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4264,61 +4264,61 @@
         <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>5.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="AU15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.52</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.58</v>
+        <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="BC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG15" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.2</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4330,25 +4330,25 @@
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4375,14 +4375,14 @@
         <v>6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="CA15" t="n">
         <v>4.9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -4443,10 +4443,10 @@
         <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.32</v>
@@ -4455,28 +4455,28 @@
         <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z16" t="n">
         <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB16" t="n">
         <v>9.6</v>
@@ -4494,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -4515,7 +4515,7 @@
         <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO16" t="n">
         <v>120</v>
@@ -4524,25 +4524,25 @@
         <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -4551,92 +4551,92 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6</v>
       </c>
-      <c r="BE16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO16" t="n">
         <v>3.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW16" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>14</v>
       </c>
       <c r="BX16" t="n">
         <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA16" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -4685,16 +4685,16 @@
         <v>3.15</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P17" t="n">
         <v>1.54</v>
@@ -4709,10 +4709,10 @@
         <v>5.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
@@ -4724,10 +4724,10 @@
         <v>8.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
         <v>80</v>
@@ -4742,7 +4742,7 @@
         <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
         <v>14</v>
@@ -4754,10 +4754,10 @@
         <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>38</v>
@@ -4766,7 +4766,7 @@
         <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="n">
         <v>42</v>
@@ -4784,16 +4784,16 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
         <v>50</v>
@@ -4808,7 +4808,7 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
         <v>32</v>
@@ -4820,77 +4820,77 @@
         <v>55</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>34</v>
       </c>
       <c r="BG17" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="BH17" t="n">
         <v>2.66</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BJ17" t="n">
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT17" t="n">
         <v>6.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>55</v>
       </c>
       <c r="CA17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -4921,85 +4921,85 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="G18" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AA18" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
         <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -5008,10 +5008,10 @@
         <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
         <v>17.5</v>
@@ -5020,131 +5020,131 @@
         <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="n">
         <v>9.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>270</v>
+        <v>420</v>
       </c>
       <c r="AP18" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS18" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>6.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX18" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
         <v>12</v>
       </c>
-      <c r="BK18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>12</v>
       </c>
-      <c r="BN18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BZ18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA18" t="n">
         <v>7.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I19" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>3.45</v>
@@ -5208,10 +5208,10 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
         <v>2.84</v>
@@ -5223,10 +5223,10 @@
         <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -5235,28 +5235,28 @@
         <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
         <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>19</v>
@@ -5265,10 +5265,10 @@
         <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
         <v>44</v>
@@ -5277,19 +5277,19 @@
         <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AS19" t="n">
         <v>4.3</v>
@@ -5301,13 +5301,13 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -5319,10 +5319,10 @@
         <v>4.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>4.3</v>
@@ -5331,10 +5331,10 @@
         <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.7</v>
+        <v>14.5</v>
       </c>
       <c r="BH19" t="n">
         <v>3.95</v>
@@ -5346,34 +5346,34 @@
         <v>9.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN19" t="n">
         <v>6.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU19" t="n">
         <v>4.4</v>
@@ -5382,13 +5382,13 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.72</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -5441,7 +5441,7 @@
         <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
         <v>4.4</v>
@@ -5450,10 +5450,10 @@
         <v>1.36</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
@@ -5462,13 +5462,13 @@
         <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>1.81</v>
@@ -5480,7 +5480,7 @@
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -5492,7 +5492,7 @@
         <v>46</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB20" t="n">
         <v>11</v>
@@ -5504,10 +5504,10 @@
         <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -5519,22 +5519,22 @@
         <v>70</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
         <v>12.5</v>
@@ -5546,19 +5546,19 @@
         <v>4.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX20" t="n">
         <v>8.199999999999999</v>
@@ -5570,89 +5570,89 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
         <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP20" t="n">
         <v>12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -5683,55 +5683,55 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.85</v>
       </c>
-      <c r="G21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="W21" t="n">
         <v>1.32</v>
@@ -5743,10 +5743,10 @@
         <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AB21" t="n">
         <v>950</v>
@@ -5758,10 +5758,10 @@
         <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
         <v>950</v>
@@ -5770,143 +5770,143 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL21" t="n">
         <v>60</v>
       </c>
-      <c r="AL21" t="n">
-        <v>65</v>
-      </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO21" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AR21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.94</v>
+        <v>2.34</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="AX21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AY21" t="n">
         <v>3</v>
       </c>
-      <c r="AY21" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AZ21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
         <v>1.19</v>
       </c>
-      <c r="BN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BT21" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -5946,43 +5946,43 @@
         <v>2.88</v>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.27</v>
       </c>
       <c r="M22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
         <v>5.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
         <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="V22" t="n">
         <v>1.41</v>
@@ -5991,10 +5991,10 @@
         <v>1.71</v>
       </c>
       <c r="X22" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>30</v>
@@ -6003,25 +6003,25 @@
         <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF22" t="n">
         <v>21</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
         <v>38</v>
@@ -6045,58 +6045,58 @@
         <v>22</v>
       </c>
       <c r="AP22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>1.05</v>
       </c>
       <c r="AR22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>11.5</v>
+        <v>1.05</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>1.05</v>
       </c>
       <c r="AW22" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11.5</v>
+        <v>1.05</v>
       </c>
       <c r="BA22" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>14</v>
+        <v>1.05</v>
       </c>
       <c r="BH22" t="n">
         <v>4.7</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -6200,13 +6200,13 @@
         <v>5.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.5</v>
@@ -6218,13 +6218,13 @@
         <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R23" t="n">
         <v>1.26</v>
@@ -6233,7 +6233,7 @@
         <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
         <v>1.83</v>
@@ -6242,10 +6242,10 @@
         <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y23" t="n">
         <v>16</v>
@@ -6305,10 +6305,10 @@
         <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
@@ -6320,7 +6320,7 @@
         <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX23" t="n">
         <v>8.6</v>
@@ -6329,10 +6329,10 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB23" t="n">
         <v>17</v>
@@ -6344,31 +6344,31 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF23" t="n">
         <v>14.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH23" t="n">
         <v>3.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BJ23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN23" t="n">
         <v>4.4</v>
@@ -6377,44 +6377,44 @@
         <v>3.7</v>
       </c>
       <c r="BP23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BR23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BT23" t="n">
         <v>9</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY23" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>1.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="H24" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="I24" t="n">
         <v>990</v>
       </c>
       <c r="J24" t="n">
-        <v>1.09</v>
+        <v>2.68</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -6481,10 +6481,10 @@
         <v>1.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,10 +6493,10 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.41</v>
@@ -881,70 +881,70 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
         <v>36</v>
@@ -959,100 +959,100 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BH2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>6.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
         <v>7.2</v>
@@ -1061,26 +1061,26 @@
         <v>5.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CA2" t="n">
         <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
         <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
         <v>3.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -1135,25 +1135,25 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
         <v>2.1</v>
@@ -1168,7 +1168,7 @@
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
         <v>27</v>
@@ -1180,43 +1180,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
         <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
@@ -1228,10 +1228,10 @@
         <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
@@ -1246,7 +1246,7 @@
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>16.5</v>
@@ -1261,80 +1261,80 @@
         <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE3" t="n">
         <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
@@ -1383,46 +1383,46 @@
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
         <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
@@ -1434,7 +1434,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
@@ -1449,13 +1449,13 @@
         <v>9.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1467,19 +1467,19 @@
         <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP4" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS4" t="n">
         <v>42</v>
@@ -1488,10 +1488,10 @@
         <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>55</v>
@@ -1515,37 +1515,37 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
         <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH4" t="n">
         <v>3.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
         <v>3.95</v>
@@ -1554,41 +1554,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -1619,172 +1619,172 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
         <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.199999999999999</v>
@@ -1808,10 +1808,10 @@
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS5" t="n">
         <v>5.8</v>
@@ -1820,29 +1820,29 @@
         <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
         <v>16.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BY5" t="n">
         <v>5.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -1879,55 +1879,55 @@
         <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.45</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
         <v>13.5</v>
@@ -1939,7 +1939,7 @@
         <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
@@ -1951,7 +1951,7 @@
         <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1975,16 +1975,16 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
         <v>23</v>
@@ -1993,10 +1993,10 @@
         <v>65</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
@@ -2011,10 +2011,10 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -2026,19 +2026,19 @@
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>110</v>
       </c>
       <c r="BN6" t="n">
         <v>5</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,67 +2118,67 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Vikingur Olafsvik</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>5.1</v>
+        <v>2.14</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2187,177 +2187,177 @@
         <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>470</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AH7" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.28</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UMF Tindstoll</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>1.91</v>
       </c>
       <c r="I8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X8" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="BC8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR8" t="n">
         <v>24</v>
       </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BS8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX8" t="n">
         <v>17.5</v>
       </c>
-      <c r="AU8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>38</v>
-      </c>
       <c r="BY8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="U9" t="n">
-        <v>2.58</v>
+        <v>3.55</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR9" t="n">
         <v>15</v>
       </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW9" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AX9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC9" t="n">
         <v>15</v>
       </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BE9" t="n">
         <v>21</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BS9" t="n">
         <v>6.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>1.39</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="S10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="U10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W10" t="n">
         <v>3.5</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.73</v>
-      </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD10" t="n">
         <v>42</v>
       </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>65</v>
       </c>
       <c r="AN10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO10" t="n">
         <v>55</v>
       </c>
-      <c r="AO10" t="n">
-        <v>600</v>
-      </c>
       <c r="AP10" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.6</v>
+        <v>22</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.14</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.26</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI10" t="n">
         <v>5.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS10" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="R11" t="n">
         <v>2.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="X11" t="n">
-        <v>250</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>230</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN11" t="n">
         <v>55</v>
       </c>
-      <c r="AN11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AO11" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>3.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>2.28</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>26</v>
+        <v>3.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>17.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>13.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>23</v>
+        <v>2.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>21</v>
+        <v>2.56</v>
       </c>
       <c r="BF11" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BV11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,67 +3388,67 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="H12" t="n">
-        <v>1.91</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="S12" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="T12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.95</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>3.05</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3457,177 +3457,177 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AB12" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>15</v>
       </c>
-      <c r="AD12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="BA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD12" t="n">
         <v>13.5</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="BE12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI12" t="n">
         <v>6</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BQ12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BT12" t="n">
         <v>15</v>
       </c>
-      <c r="AX12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BU12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BZ12" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vikingur Olafsvik</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U13" t="n">
         <v>4.7</v>
       </c>
-      <c r="K13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.72</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
       </c>
       <c r="CA13" t="n">
         <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.45</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="T14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W14" t="n">
         <v>2.06</v>
       </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB14" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
         <v>85</v>
       </c>
-      <c r="AH14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>500</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>8.4</v>
+        <v>95</v>
       </c>
       <c r="AP14" t="n">
         <v>11</v>
       </c>
       <c r="AQ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BT14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY14" t="n">
+      <c r="BU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BX14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BZ14" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.18</v>
       </c>
-      <c r="I15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="U15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG15" t="n">
         <v>15</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X15" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>210</v>
       </c>
       <c r="AN15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD15" t="n">
         <v>55</v>
       </c>
-      <c r="AO15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK15" t="n">
         <v>6.6</v>
       </c>
-      <c r="AW15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ15" t="n">
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT15" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K16" t="n">
         <v>5.3</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AA16" t="n">
-        <v>160</v>
+        <v>480</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="AJ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR16" t="n">
         <v>22</v>
       </c>
-      <c r="AK16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AX16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD16" t="n">
+      <c r="BH16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF16" t="n">
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT16" t="n">
         <v>13</v>
       </c>
-      <c r="BG16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BU16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fort Wayne FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.72</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>5.7</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="X17" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
         <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AK17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AR17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW17" t="n">
         <v>20</v>
       </c>
-      <c r="AS17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>50</v>
-      </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>4.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>55</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,187 +4912,187 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>10</v>
       </c>
-      <c r="I18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X18" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>480</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>13</v>
-      </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,57 +5101,57 @@
         <v>13</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BP18" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ18" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Westchester SC</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fort Wayne FC</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.54</v>
+        <v>3.85</v>
       </c>
       <c r="G19" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.34</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="W19" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO19" t="n">
         <v>22</v>
       </c>
-      <c r="Y19" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>24</v>
-      </c>
       <c r="AP19" t="n">
-        <v>13</v>
+        <v>3.95</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS19" t="n">
         <v>4.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BA19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.4</v>
+        <v>1.23</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.2</v>
+        <v>1.24</v>
       </c>
       <c r="BT19" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7</v>
+        <v>1.26</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Union Omaha</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>1.05</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X20" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BH20" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BI20" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO20" t="n">
         <v>4.5</v>
       </c>
-      <c r="BO20" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BP20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>El Paso Locomotive FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.55</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K21" t="n">
         <v>4.2</v>
       </c>
-      <c r="H21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.81</v>
+        <v>1.34</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="X21" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AA21" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>60</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.72</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.34</v>
+        <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.66</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.56</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.48</v>
+        <v>17.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.44</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.15</v>
+        <v>14.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.15</v>
+        <v>7.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="BT21" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.19</v>
+        <v>9</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Union Omaha</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.14</v>
       </c>
-      <c r="G22" t="n">
+      <c r="U22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI22" t="n">
         <v>2.42</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X22" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="BJ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV22" t="n">
         <v>60</v>
       </c>
-      <c r="AB22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE22" t="n">
+      <c r="BW22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>34</v>
       </c>
-      <c r="AF22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0</v>
-      </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Boise Cutthroats FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Richmond Kickers</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="G23" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>990</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="X23" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,244 +6431,498 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Boise Cutthroats FC</t>
+          <t>Monterey Bay FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Richmond Kickers</t>
+          <t>Sporting Club Jacksonville</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="G24" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>990</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS24" t="n">
         <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW24" t="n">
         <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
         <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE24" t="n">
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG24" t="n">
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Louisville FC</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,67 +857,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -929,28 +929,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
         <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="AL2" t="n">
         <v>85</v>
@@ -959,128 +959,128 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>19</v>
-      </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV2" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -1114,49 +1114,49 @@
         <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.35</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1168,13 +1168,13 @@
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
         <v>9.199999999999999</v>
@@ -1195,7 +1195,7 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
@@ -1204,7 +1204,7 @@
         <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>40</v>
@@ -1216,7 +1216,7 @@
         <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
@@ -1228,7 +1228,7 @@
         <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1249,7 +1249,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
         <v>50</v>
@@ -1258,7 +1258,7 @@
         <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
@@ -1270,71 +1270,71 @@
         <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM3" t="n">
-        <v>15.5</v>
+        <v>100</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW3" t="n">
         <v>11.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -1365,85 +1365,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
         <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
         <v>9.4</v>
@@ -1452,52 +1452,52 @@
         <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AS4" t="n">
         <v>42</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
@@ -1506,89 +1506,89 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
         <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -1619,172 +1619,172 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H5" t="n">
         <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
         <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
         <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.199999999999999</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN5" t="n">
         <v>7.2</v>
@@ -1808,41 +1808,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR5" t="n">
         <v>19.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BT5" t="n">
         <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>16.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
         <v>19.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>10</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
         <v>3.85</v>
@@ -1888,55 +1888,55 @@
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>8.800000000000001</v>
@@ -1957,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
@@ -1969,16 +1969,16 @@
         <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
         <v>19.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -1990,13 +1990,13 @@
         <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
         <v>22</v>
@@ -2032,22 +2032,22 @@
         <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM6" t="n">
         <v>110</v>
@@ -2062,48 +2062,48 @@
         <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR6" t="n">
         <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
         <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,67 +2118,67 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vikingur Olafsvik</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="I7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2193,7 +2193,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
         <v>42</v>
@@ -2205,10 +2205,10 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG7" t="n">
         <v>970</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>36</v>
       </c>
       <c r="AH7" t="n">
         <v>970</v>
@@ -2220,7 +2220,7 @@
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
@@ -2229,135 +2229,135 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AR7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7</v>
-      </c>
       <c r="BA7" t="n">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>2.98</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hviti Riddarinn</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>3.85</v>
+        <v>1.41</v>
       </c>
       <c r="H8" t="n">
-        <v>1.91</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.06</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP8" t="n">
         <v>8.6</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X8" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>23</v>
-      </c>
       <c r="BQ8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>7.2</v>
       </c>
-      <c r="BR8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CA8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>2.22</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.01</v>
       </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z9" t="n">
         <v>160</v>
       </c>
-      <c r="Y9" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>48</v>
-      </c>
       <c r="AA9" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK9" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>70</v>
       </c>
       <c r="AL9" t="n">
         <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>50</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AP9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AW9" t="n">
-        <v>17.5</v>
+        <v>38</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BE9" t="n">
         <v>21</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.4</v>
+        <v>60</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UMF Tindstoll</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="H10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="S10" t="n">
         <v>1.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="U10" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Y10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Z10" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AA10" t="n">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>22</v>
       </c>
-      <c r="AD10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AK10" t="n">
         <v>17</v>
       </c>
-      <c r="AG10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AL10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP10" t="n">
         <v>65</v>
       </c>
-      <c r="AN10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
         <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW10" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BF10" t="n">
         <v>2.74</v>
       </c>
       <c r="BG10" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
         <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.16</v>
@@ -3170,210 +3170,210 @@
         <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
         <v>4.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="R11" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="T11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>250</v>
       </c>
       <c r="Y11" t="n">
         <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>15.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="n">
-        <v>55</v>
+        <v>9.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.5</v>
+        <v>44</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.6</v>
+        <v>19</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.28</v>
+        <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.56</v>
+        <v>14.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="G12" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>8.4</v>
+        <v>2.02</v>
       </c>
       <c r="J12" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU12" t="n">
         <v>11.5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="AV12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI12" t="n">
         <v>4.7</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="BJ12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP12" t="n">
         <v>23</v>
       </c>
-      <c r="AD12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR12" t="n">
+      <c r="BQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BU12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BY12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
+      <c r="BZ12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CA12" t="n">
         <v>5</v>
       </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>4.1</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Vikingur Olafsvik</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T13" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.76</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>3.35</v>
+        <v>46</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>3.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>4.8</v>
       </c>
-      <c r="I14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="AX14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU14" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="BV14" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="BW14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX14" t="n">
         <v>22</v>
       </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="BY14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>27</v>
-      </c>
       <c r="CA14" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>16</v>
       </c>
       <c r="O15" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="P15" t="n">
-        <v>1.54</v>
+        <v>6.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.74</v>
+        <v>1.14</v>
       </c>
       <c r="R15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.2</v>
       </c>
-      <c r="S15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.18</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW15" t="n">
         <v>10</v>
       </c>
-      <c r="Z15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="AX15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA15" t="n">
         <v>9</v>
       </c>
-      <c r="AR15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>36</v>
-      </c>
       <c r="BB15" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>55</v>
+        <v>5.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>25</v>
+        <v>4.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="H16" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="X16" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Westchester SC</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fort Wayne FC</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.54</v>
+        <v>1.41</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94</v>
+        <v>1.47</v>
       </c>
       <c r="H17" t="n">
-        <v>2.56</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>11.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.34</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.52</v>
+        <v>3.1</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="AA17" t="n">
-        <v>48</v>
+        <v>550</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
         <v>34</v>
       </c>
-      <c r="AF17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>19</v>
-      </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="AJ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL17" t="n">
         <v>50</v>
       </c>
-      <c r="AK17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>44</v>
-      </c>
       <c r="AM17" t="n">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>430</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.6</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC17" t="n">
         <v>14</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,34 +4912,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Fort Wayne FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="G18" t="n">
-        <v>1.76</v>
+        <v>2.86</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="I18" t="n">
-        <v>5.7</v>
+        <v>2.96</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4948,210 +4948,210 @@
         <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z18" t="n">
         <v>22</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
         <v>24</v>
       </c>
-      <c r="Z18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AO18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
+      <c r="BA18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BC18" t="n">
         <v>20</v>
       </c>
-      <c r="AI18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ18" t="n">
+      <c r="BD18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7</v>
-      </c>
       <c r="BG18" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.85</v>
+        <v>1.88</v>
       </c>
       <c r="G19" t="n">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="H19" t="n">
-        <v>2.06</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
         <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>2.06</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Z19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
         <v>15</v>
       </c>
-      <c r="AA19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AO19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>28</v>
       </c>
-      <c r="AF19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA19" t="n">
-        <v>1.21</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union Omaha</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="H20" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>5.4</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.54</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>5.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>2.56</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC20" t="n">
         <v>30</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="BD20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX20" t="n">
         <v>60</v>
       </c>
-      <c r="AB20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Inter Toronto FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="I21" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="V21" t="n">
-        <v>1.34</v>
+        <v>1.86</v>
       </c>
       <c r="W21" t="n">
-        <v>1.87</v>
+        <v>1.31</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF21" t="n">
         <v>34</v>
       </c>
-      <c r="AA21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
         <v>50</v>
       </c>
-      <c r="AF21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO21" t="n">
         <v>20</v>
       </c>
-      <c r="AI21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>40</v>
-      </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>3.05</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>2.92</v>
       </c>
       <c r="AS21" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>2.96</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>3.15</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>17.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC21" t="n">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Charlotte Independence</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Union Omaha</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>2.94</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.5</v>
       </c>
-      <c r="M22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.14</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="X22" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AA22" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>14</v>
       </c>
       <c r="AR22" t="n">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>48</v>
+        <v>4.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>44</v>
+        <v>4.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="BJ22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Boise Cutthroats FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Richmond Kickers</t>
+          <t>El Paso Locomotive FC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="G23" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA23" t="n">
         <v>4.8</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Monterey Bay FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="G24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S24" t="n">
         <v>4.6</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.84</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X24" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA24" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>23</v>
       </c>
       <c r="AE24" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="BB24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE24" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH24" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,244 +6685,752 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Phoenix Rising FC</t>
+          <t>Boise Cutthroats FC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Louisville FC</t>
+          <t>Richmond Kickers</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
         <v>1.01</v>
       </c>
       <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:40:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Monterey Bay FC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X26" t="n">
         <v>25</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="Y26" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN26" t="n">
         <v>10.5</v>
       </c>
-      <c r="BH25" t="n">
+      <c r="AO26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:40:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Louisville FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G27" t="n">
         <v>3.75</v>
       </c>
-      <c r="BI25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ25" t="n">
+      <c r="H27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BK27" t="n">
         <v>5.9</v>
       </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN25" t="n">
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN27" t="n">
         <v>7</v>
       </c>
-      <c r="BO25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
+      <c r="BO27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT25" t="n">
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT27" t="n">
         <v>5.1</v>
       </c>
-      <c r="BU25" t="n">
+      <c r="BU27" t="n">
         <v>3.95</v>
       </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
         <v>10</v>
       </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA25" t="n">
+      <c r="BZ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA27" t="n">
         <v>9.4</v>
       </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-06-10 09:31:04</t>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-10.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>12.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>1.47</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>3.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW2" t="n">
         <v>15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AX2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>1.2</v>
       </c>
       <c r="BU2" t="n">
         <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.04</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="Z3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
       </c>
       <c r="AD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN3" t="n">
         <v>16</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>55</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>50</v>
       </c>
       <c r="BB3" t="n">
         <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="BM3" t="n">
         <v>100</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BR3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>30</v>
       </c>
-      <c r="BS3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>27</v>
-      </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -1377,218 +1377,218 @@
         <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
         <v>4.5</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
         <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>60</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
         <v>70</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -1622,61 +1622,61 @@
         <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
         <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T5" t="n">
         <v>1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="V5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.59</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.6</v>
       </c>
       <c r="X5" t="n">
         <v>70</v>
       </c>
       <c r="Y5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1685,7 +1685,7 @@
         <v>85</v>
       </c>
       <c r="AB5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AC5" t="n">
         <v>15</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AG5" t="n">
         <v>15</v>
@@ -1718,19 +1718,19 @@
         <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
         <v>21</v>
@@ -1739,25 +1739,25 @@
         <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AU5" t="n">
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
         <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1772,77 +1772,77 @@
         <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
         <v>7.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO5" t="n">
         <v>5.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.1</v>
       </c>
       <c r="BP5" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -1903,7 +1903,7 @@
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>2.14</v>
@@ -1918,13 +1918,13 @@
         <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1933,7 +1933,7 @@
         <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
         <v>80</v>
@@ -1951,25 +1951,25 @@
         <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
@@ -1984,10 +1984,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS6" t="n">
         <v>70</v>
@@ -1996,7 +1996,7 @@
         <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
@@ -2017,7 +2017,7 @@
         <v>50</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC6" t="n">
         <v>22</v>
@@ -2029,22 +2029,22 @@
         <v>85</v>
       </c>
       <c r="BF6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>18.5</v>
+        <v>50</v>
       </c>
       <c r="BH6" t="n">
         <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BL6" t="n">
         <v>140</v>
@@ -2053,50 +2053,50 @@
         <v>110</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
         <v>2.62</v>
       </c>
       <c r="I7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.14</v>
@@ -2157,28 +2157,28 @@
         <v>1.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="T7" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="U7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="V7" t="n">
         <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2235,31 +2235,31 @@
         <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
         <v>5.7</v>
@@ -2268,37 +2268,37 @@
         <v>6.8</v>
       </c>
       <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,50 +2307,50 @@
         <v>36</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -2381,82 +2381,82 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.07</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>1.22</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
         <v>1.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="X8" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y8" t="n">
         <v>75</v>
       </c>
-      <c r="Y8" t="n">
-        <v>70</v>
-      </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AA8" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB8" t="n">
         <v>26</v>
       </c>
       <c r="AC8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="n">
         <v>42</v>
       </c>
       <c r="AE8" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="AF8" t="n">
         <v>18</v>
@@ -2480,25 +2480,25 @@
         <v>26</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AO8" t="n">
         <v>44</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>17.5</v>
@@ -2510,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2522,89 +2522,89 @@
         <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
         <v>17.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BJ8" t="n">
         <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM8" t="n">
         <v>40</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="BP8" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>16.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="BT8" t="n">
         <v>14.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>2.26</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.66</v>
+        <v>5.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -2641,46 +2641,46 @@
         <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="T9" t="n">
         <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2689,176 +2689,176 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AA9" t="n">
         <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD9" t="n">
         <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM9" t="n">
         <v>55</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
       <c r="AN9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM9" t="n">
         <v>60</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.13</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.07</v>
@@ -2922,40 +2922,40 @@
         <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="U10" t="n">
         <v>3.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="X10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Y10" t="n">
         <v>90</v>
       </c>
       <c r="Z10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA10" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="AB10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AC10" t="n">
         <v>19</v>
@@ -2964,37 +2964,37 @@
         <v>34</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="n">
         <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AM10" t="n">
         <v>44</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
         <v>65</v>
@@ -3009,19 +3009,19 @@
         <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW10" t="n">
         <v>42</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
@@ -3039,28 +3039,28 @@
         <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BE10" t="n">
         <v>34</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="BG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,50 +3069,50 @@
         <v>40</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
         <v>2.92</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -3170,46 +3170,46 @@
         <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P11" t="n">
         <v>4.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
         <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
         <v>250</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Z11" t="n">
         <v>85</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AC11" t="n">
         <v>15.5</v>
@@ -3221,28 +3221,28 @@
         <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
         <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ11" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AM11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN11" t="n">
         <v>9.4</v>
@@ -3254,16 +3254,16 @@
         <v>44</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>16.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AU11" t="n">
         <v>12.5</v>
@@ -3272,49 +3272,49 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
         <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF11" t="n">
         <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,50 +3323,50 @@
         <v>38</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
         <v>3.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I12" t="n">
         <v>2.02</v>
@@ -3412,10 +3412,10 @@
         <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3427,22 +3427,22 @@
         <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1.32</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="S12" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.98</v>
@@ -3454,7 +3454,7 @@
         <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
         <v>55</v>
@@ -3463,31 +3463,31 @@
         <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AF12" t="n">
         <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
         <v>42</v>
@@ -3499,22 +3499,22 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
         <v>19</v>
       </c>
       <c r="AR12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
         <v>23</v>
@@ -3529,10 +3529,10 @@
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
@@ -3541,7 +3541,7 @@
         <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
         <v>24</v>
@@ -3553,10 +3553,10 @@
         <v>24</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="n">
         <v>6.2</v>
@@ -3568,10 +3568,10 @@
         <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM12" t="n">
         <v>40</v>
@@ -3580,7 +3580,7 @@
         <v>8.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP12" t="n">
         <v>23</v>
@@ -3595,10 +3595,10 @@
         <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV12" t="n">
         <v>12.5</v>
@@ -3610,17 +3610,17 @@
         <v>17.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -3678,7 +3678,7 @@
         <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
         <v>3.1</v>
@@ -3690,19 +3690,19 @@
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="U13" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,31 +3711,31 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AF13" t="n">
         <v>30</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
@@ -3744,7 +3744,7 @@
         <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -3753,19 +3753,19 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
@@ -3777,10 +3777,10 @@
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3792,7 +3792,7 @@
         <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
         <v>10.5</v>
@@ -3801,28 +3801,28 @@
         <v>9</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,50 +3831,50 @@
         <v>46</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G14" t="n">
         <v>4.7</v>
@@ -3917,7 +3917,7 @@
         <v>1.94</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
         <v>5</v>
@@ -3926,7 +3926,7 @@
         <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
         <v>5.5</v>
@@ -3938,19 +3938,19 @@
         <v>2.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R14" t="n">
         <v>1.69</v>
       </c>
       <c r="S14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3992,7 +3992,7 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AJ14" t="n">
         <v>500</v>
@@ -4004,67 +4004,67 @@
         <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
         <v>32</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.1</v>
+        <v>18.5</v>
       </c>
       <c r="AU14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="n">
         <v>4.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1.11</v>
@@ -4189,25 +4189,25 @@
         <v>1.04</v>
       </c>
       <c r="P15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Q15" t="n">
         <v>1.14</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
         <v>1.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
         <v>1.52</v>
@@ -4216,10 +4216,10 @@
         <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AA15" t="n">
         <v>500</v>
@@ -4231,22 +4231,22 @@
         <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
         <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AH15" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="AJ15" t="n">
         <v>500</v>
@@ -4255,82 +4255,82 @@
         <v>180</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AP15" t="n">
         <v>100</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK15" t="n">
         <v>6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4339,50 +4339,50 @@
         <v>24</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -4416,61 +4416,61 @@
         <v>1.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
         <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
         <v>55</v>
@@ -4479,25 +4479,25 @@
         <v>160</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>85</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
         <v>80</v>
@@ -4509,134 +4509,134 @@
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP16" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC16" t="n">
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF16" t="n">
         <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
         <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO16" t="n">
         <v>3.45</v>
       </c>
       <c r="BP16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G17" t="n">
         <v>1.47</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
         <v>5.1</v>
@@ -4688,52 +4688,52 @@
         <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
         <v>1.98</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
         <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA17" t="n">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
         <v>11.5</v>
@@ -4742,7 +4742,7 @@
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AF17" t="n">
         <v>8.6</v>
@@ -4754,37 +4754,37 @@
         <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS17" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>430</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
         <v>6.2</v>
@@ -4793,7 +4793,7 @@
         <v>8.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AW17" t="n">
         <v>9.199999999999999</v>
@@ -4808,7 +4808,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB17" t="n">
         <v>10</v>
@@ -4823,74 +4823,74 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -4921,220 +4921,220 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="G18" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="X18" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB18" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AC18" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
         <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="BG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5193,19 +5193,19 @@
         <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
         <v>2.14</v>
@@ -5214,16 +5214,16 @@
         <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U19" t="n">
         <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
         <v>2.06</v>
@@ -5235,7 +5235,7 @@
         <v>15.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
         <v>130</v>
@@ -5244,10 +5244,10 @@
         <v>8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>70</v>
@@ -5256,13 +5256,13 @@
         <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
         <v>21</v>
@@ -5274,13 +5274,13 @@
         <v>42</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP19" t="n">
         <v>11</v>
@@ -5289,13 +5289,13 @@
         <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
         <v>7.4</v>
@@ -5304,19 +5304,19 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AX19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB19" t="n">
         <v>19</v>
@@ -5328,77 +5328,77 @@
         <v>36</v>
       </c>
       <c r="BE19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>17.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>70</v>
       </c>
       <c r="BH19" t="n">
         <v>3.25</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL19" t="n">
         <v>150</v>
       </c>
       <c r="BM19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP19" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX19" t="n">
         <v>55</v>
       </c>
       <c r="BY19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
         <v>2.58</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.6</v>
@@ -5453,7 +5453,7 @@
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.57</v>
@@ -5468,28 +5468,28 @@
         <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
         <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
         <v>75</v>
@@ -5501,16 +5501,16 @@
         <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
         <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -5519,22 +5519,22 @@
         <v>85</v>
       </c>
       <c r="AJ20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK20" t="n">
         <v>40</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>38</v>
       </c>
       <c r="AL20" t="n">
         <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP20" t="n">
         <v>7.6</v>
@@ -5543,7 +5543,7 @@
         <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
         <v>60</v>
@@ -5558,101 +5558,101 @@
         <v>14.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>70</v>
+        <v>17.5</v>
       </c>
       <c r="BB20" t="n">
         <v>32</v>
       </c>
       <c r="BC20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD20" t="n">
         <v>55</v>
       </c>
       <c r="BE20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BF20" t="n">
         <v>34</v>
       </c>
       <c r="BG20" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BN20" t="n">
         <v>5.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP20" t="n">
         <v>23</v>
       </c>
       <c r="BQ20" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR20" t="n">
         <v>46</v>
       </c>
       <c r="BS20" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV20" t="n">
         <v>34</v>
       </c>
       <c r="BW20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -5683,58 +5683,58 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.8</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.31</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -5746,7 +5746,7 @@
         <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB21" t="n">
         <v>950</v>
@@ -5758,7 +5758,7 @@
         <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
         <v>34</v>
@@ -5770,143 +5770,143 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL21" t="n">
         <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO21" t="n">
         <v>20</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AV21" t="n">
         <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="BC21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH21" t="n">
         <v>3.45</v>
       </c>
-      <c r="BD21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -5958,22 +5958,22 @@
         <v>1.27</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
         <v>1.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S22" t="n">
         <v>2.4</v>
@@ -5985,7 +5985,7 @@
         <v>2.56</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
         <v>1.71</v>
@@ -6048,7 +6048,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AR22" t="n">
         <v>4.5</v>
@@ -6087,7 +6087,7 @@
         <v>4.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
         <v>4.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -6191,187 +6191,187 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H23" t="n">
         <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y23" t="n">
         <v>22</v>
       </c>
-      <c r="Y23" t="n">
-        <v>20</v>
-      </c>
       <c r="Z23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF23" t="n">
         <v>15</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>38</v>
       </c>
       <c r="AM23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AR23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS23" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>5</v>
-      </c>
       <c r="AT23" t="n">
-        <v>3.65</v>
+        <v>9.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO23" t="n">
         <v>3.75</v>
@@ -6380,13 +6380,13 @@
         <v>13</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT23" t="n">
         <v>7.8</v>
@@ -6398,23 +6398,23 @@
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
         <v>11</v>
       </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BZ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA23" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
         <v>3.55</v>
@@ -6463,7 +6463,7 @@
         <v>3.65</v>
       </c>
       <c r="L24" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
@@ -6472,16 +6472,16 @@
         <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P24" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
         <v>4.6</v>
@@ -6493,19 +6493,19 @@
         <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W24" t="n">
         <v>2.12</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y24" t="n">
         <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA24" t="n">
         <v>160</v>
@@ -6517,7 +6517,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>90</v>
@@ -6544,16 +6544,16 @@
         <v>50</v>
       </c>
       <c r="AM24" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AN24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO24" t="n">
         <v>140</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>13.5</v>
@@ -6562,19 +6562,19 @@
         <v>34</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AX24" t="n">
         <v>9</v>
@@ -6586,7 +6586,7 @@
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="BB24" t="n">
         <v>18</v>
@@ -6598,77 +6598,77 @@
         <v>44</v>
       </c>
       <c r="BE24" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG24" t="n">
         <v>15</v>
       </c>
-      <c r="BG24" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW24" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G25" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H25" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I25" t="n">
         <v>65</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,22 +6723,22 @@
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6747,10 +6747,10 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -6956,61 +6956,61 @@
         <v>1.71</v>
       </c>
       <c r="G26" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K26" t="n">
         <v>4.8</v>
       </c>
-      <c r="I26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.24</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
         <v>50</v>
@@ -7019,7 +7019,7 @@
         <v>140</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC26" t="n">
         <v>12.5</v>
@@ -7028,7 +7028,7 @@
         <v>25</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF26" t="n">
         <v>14</v>
@@ -7037,52 +7037,52 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN26" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.8</v>
+        <v>14.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX26" t="n">
         <v>10</v>
@@ -7091,92 +7091,92 @@
         <v>8.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.8</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.65</v>
+        <v>15.5</v>
       </c>
       <c r="BC26" t="n">
         <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG26" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG26" t="n">
+      <c r="BH26" t="n">
         <v>4.2</v>
       </c>
-      <c r="BH26" t="n">
-        <v>4</v>
-      </c>
       <c r="BI26" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN26" t="n">
         <v>4.7</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT26" t="n">
         <v>8.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -7207,58 +7207,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G27" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H27" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I27" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J27" t="n">
         <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O27" t="n">
         <v>1.27</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
         <v>1.81</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
         <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="W27" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
@@ -7267,28 +7267,28 @@
         <v>14</v>
       </c>
       <c r="Z27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
         <v>34</v>
       </c>
       <c r="AB27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH27" t="n">
         <v>21</v>
@@ -7297,43 +7297,43 @@
         <v>42</v>
       </c>
       <c r="AJ27" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
         <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO27" t="n">
         <v>17.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>3.65</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
         <v>19.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW27" t="n">
         <v>16</v>
@@ -7342,34 +7342,34 @@
         <v>19.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD27" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI27" t="n">
         <v>3</v>
@@ -7378,13 +7378,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN27" t="n">
         <v>7</v>
@@ -7396,7 +7396,7 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
@@ -7405,7 +7405,7 @@
         <v>11</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU27" t="n">
         <v>3.95</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
